--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Foresight validated against real clinical trials both retrospectively and prospectively (multiple validations). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Check sizes below are Unknown pending PitchBook; all personal emails are inferred, not verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors).</t>
+          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor).</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3083,22 +3083,22 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Unknown (confirm fund size/vintage)</t>
+          <t>Fund II, ~$230M, closed Jan 2025 (~$1B AUM reported 2026)</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Seed and early; applied AI (Software 3.0)</t>
+          <t>Seed/first-round leads; applied and vertical AI</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>$1M to $25M, often first investor</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Yes (confirm)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Applied-AI generalist; life-science exposure not confirmed. Verify any bio holdings.</t>
+          <t>Health is a named sector: OpenEvidence (clinical decision support, reported ~$12B valuation Jan 2026). Thesis explicitly names biology as a domain needing specialized data.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Pure applied-AI thesis (Software 3.0, AI-native apps and agents). iViz workbench plus Mona/Merlin agents map to the thesis.</t>
+          <t>Pure applied/vertical-AI thesis (names biology, materials, physical simulation). AI-native portfolio: Harvey, Sierra, Cognition, Mistral, Baseten. iViz workbench plus Mona/Merlin agents map to the thesis.</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Confirm portfolio before Tier assignment.</t>
+          <t>OpenEvidence (clinical Q&amp;A/decision support, not a Foresight or iViz competitor).</t>
         </is>
       </c>
       <c r="L18" s="9" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>Founder and General Partner</t>
+          <t>Founder and General Partner (alt: Mike Vernal, GP, infra/PLG for iViz)</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
@@ -3145,30 +3145,30 @@
         </is>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>5</v>
       </c>
       <c r="S18" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" s="9" t="n">
         <v>4</v>
-      </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W18" s="10">
         <f>MAX(0,ROUND(Q18/5*Weights!$B$3+R18/5*Weights!$B$4+S18/5*Weights!$B$5+T18/5*Weights!$B$6+U18/5*Weights!$B$7+V18/5*Weights!$B$8-L18*Weights!$B$9,0))</f>
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="X18" s="10" t="str">
         <f>IF(W18&gt;=Weights!$B$12,"A",IF(W18&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Y18" s="11" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AA18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY: fund status, recent deals, best contact path, email.</t>
+          <t>Lead with the Applied-AI + AI-for-science story; confirm personal email.</t>
         </is>
       </c>
       <c r="AB18" s="7" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AC18" s="8" t="inlineStr">
         <is>
-          <t>https://www.conviction.com/</t>
+          <t>https://www.forbes.com/sites/alexkonrad/2025/01/31/inside-venture-capital-great-reshuffling/; https://saranormous.substack.com/p/launching-with-conviction</t>
         </is>
       </c>
       <c r="AD18" s="8" t="inlineStr">
         <is>
-          <t>NEW candidate, not yet verified this pass. Added for the applied-AI (iViz + company narrative) door. Scores conservative pending verification.</t>
+          <t>Verified. Only functional inbox embed@conviction.com is confirmed; sarah@conviction.com / mike@conviction.com are inferred, LOW confidence. Mike Vernal (ex-Sequoia, PLG/infra) is a strong alt contact for the iViz self-serve angle.</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>AI-first fund</t>
+          <t>AI-first fund (AI in Sciences thesis)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Unknown (confirm fund size/vintage)</t>
+          <t>$650M early-stage AI fund (final close ~2024); $800M growth (Aug 2024); &gt;$1B first close Breakouts fund (2025); ~$1.8B AUM</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Seed to growth; AI-first incl. AI-for-science (confirm)</t>
+          <t>Leads early-stage AI (seed to Series A)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Selective (confirm)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -3244,35 +3244,35 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>AI-for-science interest with some bio exposure; confirm specific holdings.</t>
+          <t>Formal 'AI in Sciences' thesis (generative AI for biology/chemistry/physics). Holdings: Genesis Therapeutics, Nabla Bio, Aspect Biosystems, Attuned Intelligence (healthcare AI). Led Attuned $13M seed (2025).</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>AI-first fund; fits the Applied AI company narrative. Confirm portfolio depth.</t>
+          <t>AI-first fund with a published AI-in-sciences thesis and an AI-native portfolio that follows it. Strong fit for the Applied AI company narrative.</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Confirm portfolio before Tier assignment.</t>
+          <t>Unlearn.AI: AI digital-twin control arms for clinical trials, a DIRECT Foresight competitor.</t>
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unlearn.AI (digital-twin / in-silico clinical trials) competes head-on with Foresight.</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Unknown (identify AI-for-science partner)</t>
+          <t>Sanjana Basu</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partner (leads AI in Sciences; alt: Jordan Jacobs, Co-Founder/MP)</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
@@ -3281,13 +3281,13 @@
         </is>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>5</v>
       </c>
       <c r="S19" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" s="9" t="n">
         <v>0</v>
@@ -3296,11 +3296,11 @@
         <v>1</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W19" s="10">
         <f>MAX(0,ROUND(Q19/5*Weights!$B$3+R19/5*Weights!$B$4+S19/5*Weights!$B$5+T19/5*Weights!$B$6+U19/5*Weights!$B$7+V19/5*Weights!$B$8-L19*Weights!$B$9,0))</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X19" s="10" t="str">
         <f>IF(W19&gt;=Weights!$B$12,"A",IF(W19&gt;=Weights!$B$13,"B","C"))</f>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AA19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY: partner, recent deals, fund status, contact.</t>
+          <t>CONFLICT (Unlearn.AI): angle on iViz / applied-AI only, or deprioritize for Foresight.</t>
         </is>
       </c>
       <c r="AB19" s="7" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AC19" s="8" t="inlineStr">
         <is>
-          <t>https://radical.vc/</t>
+          <t>https://radical.vc/investing-in-the-exponential-ai-in-sciences/; https://radical.vc/team/sanjana-basu/</t>
         </is>
       </c>
       <c r="AD19" s="8" t="inlineStr">
         <is>
-          <t>NEW candidate, not yet verified this pass. Added for the applied-AI door.</t>
+          <t>Verified. Conflict penalty applied for Unlearn.AI. Absent the conflict this scores ~78 (Tier A); with it, ~53. Email inferred: sanjana@radical.vc (domain @radical.vc confirmed; convention assumed).</t>
         </is>
       </c>
     </row>
@@ -3355,22 +3355,22 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Unknown (confirm fund size/vintage)</t>
+          <t>Fund IV, $250M, closed Jan 2026 (Fund III $185M 2024)</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Seed, leads; AI, automation, and data tooling</t>
+          <t>Seed, leads; vertical AI, infrastructure, automated workflows</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>$2M to $3M seed (pre-seed ~$250K to $500K)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Yes (confirm)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Minimal life-science exposure; AI/automation and data-tooling focus.</t>
+          <t>Sectors explicitly include Biotech &amp; Life Sciences and Healthcare. Holdings: Cusp (CuspAI, molecular/materials foundation models), Neion (medicine), Basata (healthcare admin AI), Seen Health.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>AI/automation and data-tooling thesis; strong fit for iViz's workflow-automation angle. Confirm recent deals.</t>
+          <t>AI-native since 2017; vertical-AI, infrastructure, and automated-workflow thesis. Strong fit for iViz's data-analysis/workflow-automation angle.</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Confirm portfolio before Tier assignment.</t>
+          <t>Cusp (molecular/materials discovery, adjacent not competing); no clinical-trial-simulation or notebook/BI holding found.</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Unknown (identify data-tooling partner)</t>
+          <t>Lan Xuezhao</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Founder and Managing Partner (alt: Chang Xu, Partner)</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>5</v>
@@ -3426,21 +3426,21 @@
         <v>5</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W20" s="10">
         <f>MAX(0,ROUND(Q20/5*Weights!$B$3+R20/5*Weights!$B$4+S20/5*Weights!$B$5+T20/5*Weights!$B$6+U20/5*Weights!$B$7+V20/5*Weights!$B$8-L20*Weights!$B$9,0))</f>
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="X20" s="10" t="str">
         <f>IF(W20&gt;=Weights!$B$12,"A",IF(W20&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Y20" s="11" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="AA20" s="8" t="inlineStr">
         <is>
-          <t>VERIFY: partner, recent deals, fund status, contact.</t>
+          <t>Lead with iViz (AI data workbench); confirm basisset.com vs basisset.ventures domain before emailing.</t>
         </is>
       </c>
       <c r="AB20" s="7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="AC20" s="8" t="inlineStr">
         <is>
-          <t>https://www.basisset.com/</t>
+          <t>https://en.wikipedia.org/wiki/Basis_Set_Ventures; https://www.basisset.com/portfolio</t>
         </is>
       </c>
       <c r="AD20" s="8" t="inlineStr">
         <is>
-          <t>NEW candidate, not yet verified this pass. Best fit is iViz data-tooling, not the clinical vertical.</t>
+          <t>Verified. Email lan@basisset.com is Verified (pattern firstname@basisset.com); some databases list basisset.ventures, confirm first. $2-3M seed check fits as co-lead/participant more than a full seed lead.</t>
         </is>
       </c>
     </row>
@@ -3745,9 +3745,1233 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sanofi Ventures</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Pharma corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Evergreen; +$625M committed Sep 2025 (~$1.4B AUM)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Early-stage; leads/co-leads biotech and digital health</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Deep biotech book (Atalanta, Glycomine, Draig 2025; 3 exits 2024 ~$3.25B). Explicit digital-health and data-science vertical.</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>The $625M top-up (Sep 2025) was framed around AI; digital-health/data-science is a named vertical.</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Jason P. Hafler</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>Managing Director (early-stage biotech + AI/digital health)</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node. Strategic: also a pharma buyer/POC path.</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W23" s="10">
+        <f>MAX(0,ROUND(Q23/5*Weights!$B$3+R23/5*Weights!$B$4+S23/5*Weights!$B$5+T23/5*Weights!$B$6+U23/5*Weights!$B$7+V23/5*Weights!$B$8-L23*Weights!$B$9,0))</f>
+        <v>66</v>
+      </c>
+      <c r="X23" s="10" t="str">
+        <f>IF(W23&gt;=Weights!$B$12,"A",IF(W23&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y23" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>Approach as strategic (financial + POC); verify email.</t>
+        </is>
+      </c>
+      <c r="AB23" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/press-release-sanofi-commits-an-additional-625-million-to-sanofi-ventures-to-accelerate-investment-in-biotech-and-digital-health-innovation; https://www.zoominfo.com/p/Jason-Hafler</t>
+        </is>
+      </c>
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>CVC. Email inferred: jason.hafler@sanofi.com (ZoomInfo confirms j***@sanofi.com; Sanofi standard first.last@sanofi.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>MSD Global Health Innovation Fund (GHIF)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pharma corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Boston / Kenilworth, NJ</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Evergreen, ~$500M AUM; IDEA Studios (2024, ~$38M early-stage)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Primarily GROWTH; IDEA Studios adds early engagement</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>No (growth-stage)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Invests in digital-health and data-science companies that optimize biopharma operations, directly Coharts-adjacent.</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>AI + healthcare-data is an intensifying thesis; digital-health/data-science mandate.</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>Joel Krikston</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>Managing Director, Venture Investments</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node. Strategic: pharma buyer/POC path.</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" s="10">
+        <f>MAX(0,ROUND(Q24/5*Weights!$B$3+R24/5*Weights!$B$4+S24/5*Weights!$B$5+T24/5*Weights!$B$6+U24/5*Weights!$B$7+V24/5*Weights!$B$8-L24*Weights!$B$9,0))</f>
+        <v>60</v>
+      </c>
+      <c r="X24" s="10" t="str">
+        <f>IF(W24&gt;=Weights!$B$12,"A",IF(W24&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y24" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA24" s="8" t="inlineStr">
+        <is>
+          <t>Treat as strategic/later-round + POC, not a seed lead; verify email domain.</t>
+        </is>
+      </c>
+      <c r="AB24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.msd.com/news/msd-launches-idea-studios-to-fuel-health-care-innovation/; https://www.crunchbase.com/organization/merck-global-health-innovation-fund</t>
+        </is>
+      </c>
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>Growth-stage CVC, unlikely to lead a seed. Email inferred: joel.krikston@merck.com (or @msdghifund.com, unresolved).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Danaher Ventures</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Life-science instruments corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Corporate CVC (founded 2017)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Strategic early-stage co-investor; rarely sole seed lead</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Rarely (co-invests)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Biotech, diagnostics, life sciences, and data sciences mandate. Innovaccer partnership (Jan 2025); Scopio Labs, AI diagnostics (Jul 2025).</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare-AI deals (Innovaccer, Scopio); data-sciences is a named focus.</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Murali Venkatesan</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>VP and Head of Danaher Ventures (Americas &amp; Europe)</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node. Strategic: instruments/data ecosystem.</t>
+        </is>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" s="10">
+        <f>MAX(0,ROUND(Q25/5*Weights!$B$3+R25/5*Weights!$B$4+S25/5*Weights!$B$5+T25/5*Weights!$B$6+U25/5*Weights!$B$7+V25/5*Weights!$B$8-L25*Weights!$B$9,0))</f>
+        <v>60</v>
+      </c>
+      <c r="X25" s="10" t="str">
+        <f>IF(W25&gt;=Weights!$B$12,"A",IF(W25&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y25" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>Approach as strategic co-investor; verify email.</t>
+        </is>
+      </c>
+      <c r="AB25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.danaher.com/danaher-ventures; https://www.prnewswire.com/news-releases/danaher-announces-investment-partnership-in-innovaccer-inc-302347452.html</t>
+        </is>
+      </c>
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>CVC, strategic co-investor. Email inferred: murali.venkatesan@danaher.com (first.last@danaher.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Strategic Capital</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Life-science instruments corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Waltham, MA</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Corporate strategic-capital team</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Strategic co-investor; not a lead</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>No (co-invests)</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Life sciences, diagnostics, devices, disease modeling. Backed CytoReason (computational biology, $80M Series B) and miDiagnostics.</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Disease-modeling / computational-biology exposure (CytoReason) adjacent to Coharts' simulation story.</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>CytoReason (disease modeling for targets/biomarkers, adjacent not competing).</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>Bhooshi De Silva</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>Head of Strategic Capital (alt: Carson Massey, Associate Director)</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node. Strategic: instruments ecosystem.</t>
+        </is>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R26" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" s="10">
+        <f>MAX(0,ROUND(Q26/5*Weights!$B$3+R26/5*Weights!$B$4+S26/5*Weights!$B$5+T26/5*Weights!$B$6+U26/5*Weights!$B$7+V26/5*Weights!$B$8-L26*Weights!$B$9,0))</f>
+        <v>58</v>
+      </c>
+      <c r="X26" s="10" t="str">
+        <f>IF(W26&gt;=Weights!$B$12,"A",IF(W26&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y26" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>Approach as strategic co-investor; verify email.</t>
+        </is>
+      </c>
+      <c r="AB26" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC26" s="8" t="inlineStr">
+        <is>
+          <t>https://globalventuring.com/corporate/people/thermo-fisher-scientific-brings-massey-onboard/; https://www.cbinsights.com/investor/thermo-fisher-scientific</t>
+        </is>
+      </c>
+      <c r="AD26" s="8" t="inlineStr">
+        <is>
+          <t>CVC, strategic co-investor, not a lead. Email inferred: bhooshi.desilva@thermofisher.com (first.last@thermofisher.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>UPMC Enterprises</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Health-system venture/commercialization arm</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>$1B committed to life-sciences investing</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Leads rounds; digital health + translational science</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Led Carta Healthcare ~$18.25M Series B1 (AI clinical-data management, expanding into life sciences). Also Abridge, Astrata, Medicom.</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Explicit AI-powered clinical-data thesis; led an AI clinical-data round.</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Carta Healthcare (clinical-data abstraction expanding to life sciences, adjacent to iViz/PRISM data; watch overlap, not a notebook/BI competitor).</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>Brent Burns</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>EVP, UPMC Enterprises (confirm investment-team deal lead)</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>Plausible via clinical partnerships; no named node confirmed. Mission-aligned health system.</t>
+        </is>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" s="10">
+        <f>MAX(0,ROUND(Q27/5*Weights!$B$3+R27/5*Weights!$B$4+S27/5*Weights!$B$5+T27/5*Weights!$B$6+U27/5*Weights!$B$7+V27/5*Weights!$B$8-L27*Weights!$B$9,0))</f>
+        <v>74</v>
+      </c>
+      <c r="X27" s="10" t="str">
+        <f>IF(W27&gt;=Weights!$B$12,"A",IF(W27&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y27" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA27" s="8" t="inlineStr">
+        <is>
+          <t>Cleanest Segment B lead-fit; identify deal-team partner + email; explore PRISM/validation data angle.</t>
+        </is>
+      </c>
+      <c r="AB27" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" s="8" t="inlineStr">
+        <is>
+          <t>https://enterprises.upmc.com/resources/insights/upmc-enterprises-leads-investment-round-in-carta-healthcare-to-advance-ai-powered-clinical-data-management/</t>
+        </is>
+      </c>
+      <c r="AD27" s="8" t="inlineStr">
+        <is>
+          <t>Strongest Segment B fit (leads, AI clinical-data thesis). Email convention Unknown; do not rely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Osage University Partners (OUP)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>University-spinout fund</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Bala Cynwyd, PA</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV (launched 2023); ~$800M AUM</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Seed to late, co-invests/follows; university-IP spinouts only</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Rarely (follows)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Life sciences + tech across 100+ university partnerships; 130+ portfolio, 33 IPOs. 2025 Penn/BioNTech $50M university-IP fund.</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Invests across software/AI, but selection is gated by university-IP origin, not thesis.</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>Marc Singer</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Managing Partner (alt: Bill Harrington, MP)</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W28" s="10">
+        <f>MAX(0,ROUND(Q28/5*Weights!$B$3+R28/5*Weights!$B$4+S28/5*Weights!$B$5+T28/5*Weights!$B$6+U28/5*Weights!$B$7+V28/5*Weights!$B$8-L28*Weights!$B$9,0))</f>
+        <v>54</v>
+      </c>
+      <c r="X28" s="10" t="str">
+        <f>IF(W28&gt;=Weights!$B$12,"A",IF(W28&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y28" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>HARD GATE: only if Coharts licenses university IP. Confirm eligibility before any outreach.</t>
+        </is>
+      </c>
+      <c r="AB28" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC28" s="8" t="inlineStr">
+        <is>
+          <t>https://news.crunchbase.com/venture/osage-university-partners-raises-third-fund-for-university-research-spinouts/</t>
+        </is>
+      </c>
+      <c r="AD28" s="8" t="inlineStr">
+        <is>
+          <t>Eligibility gate: invests ONLY in startups licensing university IP, and typically co-invests. Domain @oup.vc confirmed; marc@oup.vc / msinger@oup.vc inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>The Engine Ventures</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>MIT-affiliated tough-tech fund</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Fund III, $398M, closed Jun 2024 (&gt;$1B AUM)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed to Series B, leads; MIT/research-origin tough tech</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Health + bio among sectors, but oriented to hard/deep tech (labs, materials, bio-hardware).</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>AI among sectors; origin/tough-tech preference outweighs a pure-software AI thesis.</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>Ann DeWitt</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>General Partner (life sciences/bio; alt: Michael Kearney, GP)</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W29" s="10">
+        <f>MAX(0,ROUND(Q29/5*Weights!$B$3+R29/5*Weights!$B$4+S29/5*Weights!$B$5+T29/5*Weights!$B$6+U29/5*Weights!$B$7+V29/5*Weights!$B$8-L29*Weights!$B$9,0))</f>
+        <v>54</v>
+      </c>
+      <c r="X29" s="10" t="str">
+        <f>IF(W29&gt;=Weights!$B$12,"A",IF(W29&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y29" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA29" s="8" t="inlineStr">
+        <is>
+          <t>Fit gate: strongest with an MIT/research-origin or tough-tech tie. Confirm before prioritizing.</t>
+        </is>
+      </c>
+      <c r="AB29" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/alexknapp/2024/06/18/mit-spinout-the-engine-ventures-raises-new-400-million-fund-to-tackle-techs-toughest-problems/; https://engineventures.com/about/leadership</t>
+        </is>
+      </c>
+      <c r="AD29" s="8" t="inlineStr">
+        <is>
+          <t>Prefers MIT/research-institution origin, deep/hard tech; pure-software applied-AI is a softer fit. Email inferred: ann@engineventures.com (first@engineventures.com ~85%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Alexandria Venture Investments</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Real-estate-affiliated life-science venture arm</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Pasadena, CA</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Venture affiliate of Alexandria Real Estate (NYSE: ARE)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Seed to late, co-invests via lab-tenant ecosystem; rarely sole-leads</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (avg seed ~$10M)</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Rarely (co-invests)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Very active in biotech/diagnostics (~$2.7B, 32 new companies 2024), but wet-lab/therapeutics oriented.</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Limited; some AI-clinical-workflow exposure (mediaire). Thin for a software IaaS.</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (route via venture team, not Exec Chairman Joel Marcus)</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W30" s="10">
+        <f>MAX(0,ROUND(Q30/5*Weights!$B$3+R30/5*Weights!$B$4+S30/5*Weights!$B$5+T30/5*Weights!$B$6+U30/5*Weights!$B$7+V30/5*Weights!$B$8-L30*Weights!$B$9,0))</f>
+        <v>52</v>
+      </c>
+      <c r="X30" s="10" t="str">
+        <f>IF(W30&gt;=Weights!$B$12,"A",IF(W30&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y30" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z30" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>Moderate fit (wet-lab oriented, co-invests); identify a venture-team contact.</t>
+        </is>
+      </c>
+      <c r="AB30" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC30" s="8" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/venture-capital/alexandria-venture-investments/; https://pharmashots.com/23062/know-your-investor-alexandria-venture-may25-edition/</t>
+        </is>
+      </c>
+      <c r="AD30" s="8" t="inlineStr">
+        <is>
+          <t>Wet-lab/therapeutics oriented; moderate fit for software IaaS. Best-fit partner Unknown; corporate domain likely @are.com (inferred).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Mayo Clinic Ventures / Platform</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Health-system venture + IP commercialization</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Rochester, MN</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Mayo Clinic Ventures; Platform_Accelerate + Platform_Insights (2025)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>IP commercialization + accelerator/co-invest; sole-lead seed unconfirmed</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Large-scale clinical data (26 PB) + AI-digital-health; Platform_Accelerate cohorts of AI health-tech startups.</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>AI + real-world clinical data + clinical-research applications, directly relevant to Foresight validation and iViz.</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (Mayo Clinic Ventures investment lead)</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>Plausible via clinical/data partnership (Platform_Insights); no named node.</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W31" s="10">
+        <f>MAX(0,ROUND(Q31/5*Weights!$B$3+R31/5*Weights!$B$4+S31/5*Weights!$B$5+T31/5*Weights!$B$6+U31/5*Weights!$B$7+V31/5*Weights!$B$8-L31*Weights!$B$9,0))</f>
+        <v>64</v>
+      </c>
+      <c r="X31" s="10" t="str">
+        <f>IF(W31&gt;=Weights!$B$12,"A",IF(W31&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y31" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z31" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>Pursue as validation-data + accelerator partnership as much as investment; identify contact.</t>
+        </is>
+      </c>
+      <c r="AB31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC31" s="8" t="inlineStr">
+        <is>
+          <t>https://newsnetwork.mayoclinic.org/discussion/mayo-clinic-launches-mayo-clinic-platform_insights-to-advance-digital-innovation-and-quality-improvement-across-healthcare/; https://hitconsultant.net/2025/10/14/mayo-clinic-platform_accelerate-unveils-new-cohort-of-ai-health-tech-startups/</t>
+        </is>
+      </c>
+      <c r="AD31" s="8" t="inlineStr">
+        <is>
+          <t>Strategic/accelerator + data partner (Platform_Insights) as much as investor. Specific investment contact + email Unknown; Mayo domain @mayo.edu.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD22"/>
-  <conditionalFormatting sqref="W2:W22">
+  <autoFilter ref="A1:AD31"/>
+  <conditionalFormatting sqref="W2:W31">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3760,14 +4984,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y2:Y222" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not contacted,Researching,Intro requested,Intro made,First meeting,Diligence,Term sheet,Closed,Passed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q222 R2:R222 S2:S222 T2:T222 U2:U222 V2:V222" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="Q2:Q231 R2:R231 S2:S231 T2:T231 U2:U231 V2:V231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L222" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -3968,7 +5192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4499,17 +5723,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Applied-AI thesis; Sarah Guo founder</t>
+          <t>Fund II ~$230M Jan 2025; leads; $1M-$25M checks</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Firm website</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>https://www.conviction.com/</t>
+          <t>https://www.forbes.com/sites/alexkonrad/2025/01/31/inside-venture-capital-great-reshuffling/</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -4521,22 +5745,22 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Radical Ventures</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>AI-first fund</t>
+          <t>Applied/vertical-AI thesis names biology; OpenEvidence health holding</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Firm website</t>
+          <t>Conviction / Forbes</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>https://radical.vc/</t>
+          <t>https://saranormous.substack.com/p/launching-with-conviction</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4548,22 +5772,22 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Basis Set Ventures</t>
+          <t>Radical Ventures</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>AI/automation and data-tooling thesis</t>
+          <t>Fund sizes and AUM</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Firm website</t>
+          <t>BetaKit</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>https://www.basisset.com/</t>
+          <t>https://betakit.com/radical-ventures-holds-650-million-usd-final-close-for-new-early-stage-ai-fund/</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -4575,54 +5799,378 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Catalio Capital</t>
+          <t>Radical Ventures</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Nexus Fund IV &gt;$400M Jul 2025</t>
+          <t>AI in Sciences thesis; Unlearn.AI holding</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>BusinessWire</t>
+          <t>Radical Ventures</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20250701360026/en/</t>
+          <t>https://radical.vc/investing-in-the-exponential-ai-in-sciences/</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>Basis Set Ventures</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV $250M Jan 2026; $2-3M seed checks</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Wikipedia / f4.fund</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Basis_Set_Ventures</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Basis Set Ventures</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Life-science/healthcare sectors and holdings</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Firm website</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.basisset.com/portfolio</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Catalio Capital</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Nexus Fund IV &gt;$400M Jul 2025</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>BusinessWire</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20250701360026/en/</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>5AM Ventures</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>5AM is a therapeutics biotech VC</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Firm website</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>https://5amventures.com/team/</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Sanofi Ventures</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>+$625M Sep 2025, ~$1.4B AUM; digital-health/AI vertical</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/press-release-sanofi-commits-an-additional-625-million-to-sanofi-ventures-to-accelerate-investment-in-biotech-and-digital-health-innovation</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>MSD Global Health Innovation Fund (GHIF)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>IDEA Studios 2024; digital-health/data-science mandate</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>MSD</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.msd.com/news/msd-launches-idea-studios-to-fuel-health-care-innovation/</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Danaher Ventures</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Innovaccer partnership Jan 2025; Scopio Jul 2025</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>PRNewswire / Caplight</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/danaher-announces-investment-partnership-in-innovaccer-inc-302347452.html</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Strategic Capital</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Strategic Capital team; CytoReason backing</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Global Venturing</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>https://globalventuring.com/corporate/people/thermo-fisher-scientific-brings-massey-onboard/</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>UPMC Enterprises</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Led Carta Healthcare Series B1 (AI clinical data)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>UPMC Enterprises</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>https://enterprises.upmc.com/resources/insights/upmc-enterprises-leads-investment-round-in-carta-healthcare-to-advance-ai-powered-clinical-data-management/</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Osage University Partners (OUP)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV, ~$800M AUM, university-IP mandate</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Crunchbase News</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>https://news.crunchbase.com/venture/osage-university-partners-raises-third-fund-for-university-research-spinouts/</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>The Engine Ventures</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Fund III $398M Jun 2024</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/alexknapp/2024/06/18/mit-spinout-the-engine-ventures-raises-new-400-million-fund-to-tackle-techs-toughest-problems/</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Alexandria Venture Investments</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>~$2.7B across 32 new companies in 2024</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Tracxn</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/venture-capital/alexandria-venture-investments/</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Mayo Clinic Ventures / Platform</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Platform_Insights 2025; Platform_Accelerate AI cohorts</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>https://newsnetwork.mayoclinic.org/discussion/mayo-clinic-launches-mayo-clinic-platform_insights-to-advance-digital-innovation-and-quality-improvement-across-healthcare/</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor).</t>
+          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor). WARM-PATH NODE: DLA Piper is engaged counsel (Josh Seidenfeld, ex-Cooley Digital Health chair; confirm 'Johnny Lam' role). DLA warm-path bumps applied to a16z (strong), Bessemer, Lux, Basis Set (plausible), all CONTINGENT on DLA actually making the intro. Other firms remain warm-path 1-2 pending named nodes.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>Route via an a16z bio+health portfolio founder; no named node confirmed.</t>
+          <t>STRONG via DLA Piper (engaged counsel): partner Josh Seidenfeld personally led a16z's Prosper AI health-AI financing at DLA in 2026. Confirm the intro with Seidenfeld.</t>
         </is>
       </c>
       <c r="Q3" s="9" t="n">
@@ -1117,14 +1117,14 @@
         <v>0</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" s="9" t="n">
         <v>5</v>
       </c>
       <c r="W3" s="10">
         <f>MAX(0,ROUND(Q3/5*Weights!$B$3+R3/5*Weights!$B$4+S3/5*Weights!$B$5+T3/5*Weights!$B$6+U3/5*Weights!$B$7+V3/5*Weights!$B$8-L3*Weights!$B$9,0))</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="X3" s="10" t="str">
         <f>IF(W3&gt;=Weights!$B$12,"A",IF(W3&gt;=Weights!$B$13,"B","C"))</f>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AA3" s="8" t="inlineStr">
         <is>
-          <t>Find a portfolio-founder intro to Yoo (software lens) or Rughani (AI-health).</t>
+          <t>Ask Josh Seidenfeld (DLA Piper) for a direct intro to the bio+health team.</t>
         </is>
       </c>
       <c r="AB3" s="7" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="AC3" s="8" t="inlineStr">
         <is>
-          <t>https://a16z.com/infinite-healthcare-whats-it-worth/; https://a16z.com/author/julie-yoo/</t>
+          <t>https://a16z.com/infinite-healthcare-whats-it-worth/; https://www.dlapiper.com/en-us/news/2026/06/dla-piper-advises-andreessen-horowitz-on-usd30-million-investment-in-prosper-ai</t>
         </is>
       </c>
       <c r="AD3" s="8" t="inlineStr">
         <is>
-          <t>Emails inferred/unverified: julie@a16z.com (~55%) or jyoo@a16z.com (~62%).</t>
+          <t>Warm path via DLA Piper counsel (Seidenfeld led an a16z health-AI deal); score contingent on DLA making the intro. Emails inferred/unverified: julie@a16z.com (~55%) or jyoo@a16z.com (~62%).</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>LinkedIn or a Lux portfolio founder; no named node confirmed.</t>
+          <t>PLAUSIBLE via DLA Piper: SF partner Jonathan Axelrad represents Lux in financings; intro would hand off from Seidenfeld to Axelrad. Confirm with DLA.</t>
         </is>
       </c>
       <c r="Q5" s="9" t="n">
@@ -1389,14 +1389,14 @@
         <v>0</v>
       </c>
       <c r="U5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="W5" s="10">
         <f>MAX(0,ROUND(Q5/5*Weights!$B$3+R5/5*Weights!$B$4+S5/5*Weights!$B$5+T5/5*Weights!$B$6+U5/5*Weights!$B$7+V5/5*Weights!$B$8-L5*Weights!$B$9,0))</f>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X5" s="10" t="str">
         <f>IF(W5&gt;=Weights!$B$12,"A",IF(W5&gt;=Weights!$B$13,"B","C"))</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AA5" s="8" t="inlineStr">
         <is>
-          <t>Verify a recent Shakir health/AI deal; find intro.</t>
+          <t>Ask DLA (Axelrad) about a Lux intro to Deena Shakir; verify email.</t>
         </is>
       </c>
       <c r="AB5" s="7" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AC5" s="8" t="inlineStr">
         <is>
-          <t>https://www.luxcapital.com/people; https://www.linkedin.com/in/deenashakir</t>
+          <t>https://www.luxcapital.com/people; https://www.dlapiper.com/en/people/a/jonathan-axelrad</t>
         </is>
       </c>
       <c r="AD5" s="8" t="inlineStr">
         <is>
-          <t>Adam Goulburn is at Dimension, NOT Lux. Email inferred/unverified: deena.shakir@luxcapital.com (pattern first.last ~90%).</t>
+          <t>Adam Goulburn is at Dimension, NOT Lux. Warm path via DLA partner Axelrad (represents Lux); contingent on the hand-off. Email inferred/unverified: deena.shakir@luxcapital.com (pattern first.last ~90%).</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>Kraus co-hosts healthcare content; engagement warm-up. No named node.</t>
+          <t>PLAUSIBLE via DLA Piper: Bessemer is a named DLA VC investor-client (repeat deal counsel). Ask which DLA partner currently covers the BVP relationship.</t>
         </is>
       </c>
       <c r="Q16" s="9" t="n">
@@ -2885,14 +2885,14 @@
         <v>0</v>
       </c>
       <c r="U16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>4</v>
       </c>
       <c r="W16" s="10">
         <f>MAX(0,ROUND(Q16/5*Weights!$B$3+R16/5*Weights!$B$4+S16/5*Weights!$B$5+T16/5*Weights!$B$6+U16/5*Weights!$B$7+V16/5*Weights!$B$8-L16*Weights!$B$9,0))</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X16" s="10" t="str">
         <f>IF(W16&gt;=Weights!$B$12,"A",IF(W16&gt;=Weights!$B$13,"B","C"))</f>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AA16" s="8" t="inlineStr">
         <is>
-          <t>Verify email; confirm seed appetite (BVP leans later).</t>
+          <t>Ask DLA which partner covers Bessemer; confirm seed appetite (BVP leans later).</t>
         </is>
       </c>
       <c r="AB16" s="7" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>Cold with an open inbound process; no named node.</t>
+          <t>PLAUSIBLE via DLA Piper: Basis Set GC Jennifer Lee is a DLA alum (ex-CVC co-chair); a DLA partner who overlapped with her can make a peer intro. Confirm with DLA.</t>
         </is>
       </c>
       <c r="Q20" s="9" t="n">
@@ -3429,14 +3429,14 @@
         <v>3</v>
       </c>
       <c r="U20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>5</v>
       </c>
       <c r="W20" s="10">
         <f>MAX(0,ROUND(Q20/5*Weights!$B$3+R20/5*Weights!$B$4+S20/5*Weights!$B$5+T20/5*Weights!$B$6+U20/5*Weights!$B$7+V20/5*Weights!$B$8-L20*Weights!$B$9,0))</f>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="X20" s="10" t="str">
         <f>IF(W20&gt;=Weights!$B$12,"A",IF(W20&gt;=Weights!$B$13,"B","C"))</f>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="AA20" s="8" t="inlineStr">
         <is>
-          <t>Lead with iViz (AI data workbench); confirm basisset.com vs basisset.ventures domain before emailing.</t>
+          <t>Ask DLA about an alumni intro to GC Jennifer Lee / partner Lan Xuezhao; lead with iViz.</t>
         </is>
       </c>
       <c r="AB20" s="7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="AC20" s="8" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Basis_Set_Ventures; https://www.basisset.com/portfolio</t>
+          <t>https://en.wikipedia.org/wiki/Basis_Set_Ventures; https://www.basisset.com/basis-set-faq</t>
         </is>
       </c>
       <c r="AD20" s="8" t="inlineStr">
         <is>
-          <t>Verified. Email lan@basisset.com is Verified (pattern firstname@basisset.com); some databases list basisset.ventures, confirm first. $2-3M seed check fits as co-lead/participant more than a full seed lead.</t>
+          <t>Verified. Warm path via DLA alumni tie to GC Jennifer Lee; contingent on DLA making it. Email lan@basisset.com is Verified (pattern firstname@basisset.com); some databases list basisset.ventures, confirm first. $2-3M seed check fits as co-lead/participant more than a full seed lead.</t>
         </is>
       </c>
     </row>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor). WARM-PATH NODE: DLA Piper is engaged counsel (Josh Seidenfeld, ex-Cooley Digital Health chair; confirm 'Johnny Lam' role). DLA warm-path bumps applied to a16z (strong), Bessemer, Lux, Basis Set (plausible), all CONTINGENT on DLA actually making the intro. Other firms remain warm-path 1-2 pending named nodes.</t>
+          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor). WARM-PATH NODES: (1) Josh Seidenfeld, DLA Piper partner (ex-Cooley Digital Health chair) = legal-partner intros; bumps applied to a16z (strong), Bessemer, Lux, Basis Set (plausible), all CONTINGENT on DLA making the intro. (2) Johnny (BD, life-sciences venture-banking/investor network) = a separate channel for health/life-sciences investor intros and venture debt later; NOT yet scored, pending named funds he can open. Other firms remain warm-path 1-2 pending named nodes.</t>
         </is>
       </c>
     </row>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pipeline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weights" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$31</definedName>
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Institutional Seed; target pre-money $25M to $35M (confirm target raise and lead vs participant). Coharts: An Applied AI company, IaaS (never SaaS). Two products: iViz (AI data-analysis workbench, self-serve/PLG) and Foresight (clinical trial simulation, Simulate Success Before Patient One). Traction/proof: Tempus proof-of-concept partnership; Synthon pilot; Foresight validated against real clinical trials both retrospectively and prospectively (including LEAP and TDM1). Angel round closed Aug 2026 on a legacy pre-money SAFE at a $17.5M cap. Most check sizes are Unknown pending PitchBook; personal emails are inferred unless marked Verified. None of these firms are in the HubSpot pipeline (CRM holds pharma/CRO/biotech BD accounts, not investors). CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct Foresight competitor). WARM-PATH NODES: (1) Josh Seidenfeld, DLA Piper partner (ex-Cooley Digital Health chair) = legal-partner intros; bumps applied to a16z (strong), Bessemer, Lux, Basis Set (plausible), all CONTINGENT on DLA making the intro. (2) Johnny (BD, life-sciences venture-banking/investor network) = a separate channel for health/life-sciences investor intros and venture debt later; NOT yet scored, pending named funds he can open. Other firms remain warm-path 1-2 pending named nodes.</t>
+          <t>Institutional Seed, $6M target (valuation TBD with lead; ~26 months runway). POSITIONING UPDATE per Oct 2026 deck: Coharts = drug-development INFRASTRUCTURE, 'one record per program, from first assay to filing, with the models built in.' Foresight Base is the program record ($2K/program/month; Part 11 + ICH E6(R3) data management) with modules (PRISM, ATHENA, BEAM, CTS, iViz) switching on by stage. Applied AI, IaaS (never SaaS). Now also competes with the record/eTMF vaults (Veeva, Medidata Rave, Benchling), not only simulation tools, adding a THIRD investor door: enterprise / vertical-SaaS / dev-infrastructure. Validation is RETROSPECTIVE (LEAP Phase 2, bioavailability, failures re-run); NSCLC in PoC. Traction: Tempus POC (results for JPM Jan 2027), Synthon generics pilot complete (paid conversion $250K-$415K), PRISM with 2 pediatric hospitals (FDA grant filed/pending). A $6M seed favors seed-LEADING funds; most check sizes Unknown pending PitchBook; personal emails inferred unless marked Verified. None of these firms are in the HubSpot pipeline. CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct competitor). WARM-PATH NODES: Josh Seidenfeld (DLA Piper) = legal-partner intros (bumps on a16z/Lux/Basis Set/Bessemer, contingent on DLA); Johnny = BD / life-sciences venture-banking contact coordinating the intros. Other firms remain warm-path 1-2 pending named nodes.</t>
         </is>
       </c>
     </row>
@@ -988,11 +988,11 @@
       </c>
       <c r="W2" s="10">
         <f>MAX(0,ROUND(Q2/5*Weights!$B$3+R2/5*Weights!$B$4+S2/5*Weights!$B$5+T2/5*Weights!$B$6+U2/5*Weights!$B$7+V2/5*Weights!$B$8-L2*Weights!$B$9,0))</f>
-        <v>84</v>
-      </c>
-      <c r="X2" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X2" s="10">
         <f>IF(W2&gt;=Weights!$B$12,"A",IF(W2&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y2" s="11" t="inlineStr">
         <is>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="W3" s="10">
         <f>MAX(0,ROUND(Q3/5*Weights!$B$3+R3/5*Weights!$B$4+S3/5*Weights!$B$5+T3/5*Weights!$B$6+U3/5*Weights!$B$7+V3/5*Weights!$B$8-L3*Weights!$B$9,0))</f>
-        <v>84</v>
-      </c>
-      <c r="X3" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X3" s="10">
         <f>IF(W3&gt;=Weights!$B$12,"A",IF(W3&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y3" s="11" t="inlineStr">
         <is>
@@ -1260,11 +1260,11 @@
       </c>
       <c r="W4" s="10">
         <f>MAX(0,ROUND(Q4/5*Weights!$B$3+R4/5*Weights!$B$4+S4/5*Weights!$B$5+T4/5*Weights!$B$6+U4/5*Weights!$B$7+V4/5*Weights!$B$8-L4*Weights!$B$9,0))</f>
-        <v>74</v>
-      </c>
-      <c r="X4" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X4" s="10">
         <f>IF(W4&gt;=Weights!$B$12,"A",IF(W4&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y4" s="11" t="inlineStr">
         <is>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="W5" s="10">
         <f>MAX(0,ROUND(Q5/5*Weights!$B$3+R5/5*Weights!$B$4+S5/5*Weights!$B$5+T5/5*Weights!$B$6+U5/5*Weights!$B$7+V5/5*Weights!$B$8-L5*Weights!$B$9,0))</f>
-        <v>80</v>
-      </c>
-      <c r="X5" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X5" s="10">
         <f>IF(W5&gt;=Weights!$B$12,"A",IF(W5&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y5" s="11" t="inlineStr">
         <is>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="W6" s="10">
         <f>MAX(0,ROUND(Q6/5*Weights!$B$3+R6/5*Weights!$B$4+S6/5*Weights!$B$5+T6/5*Weights!$B$6+U6/5*Weights!$B$7+V6/5*Weights!$B$8-L6*Weights!$B$9,0))</f>
-        <v>72</v>
-      </c>
-      <c r="X6" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X6" s="10">
         <f>IF(W6&gt;=Weights!$B$12,"A",IF(W6&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y6" s="11" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="W7" s="10">
         <f>MAX(0,ROUND(Q7/5*Weights!$B$3+R7/5*Weights!$B$4+S7/5*Weights!$B$5+T7/5*Weights!$B$6+U7/5*Weights!$B$7+V7/5*Weights!$B$8-L7*Weights!$B$9,0))</f>
-        <v>72</v>
-      </c>
-      <c r="X7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X7" s="10">
         <f>IF(W7&gt;=Weights!$B$12,"A",IF(W7&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y7" s="11" t="inlineStr">
         <is>
@@ -1804,11 +1804,11 @@
       </c>
       <c r="W8" s="10">
         <f>MAX(0,ROUND(Q8/5*Weights!$B$3+R8/5*Weights!$B$4+S8/5*Weights!$B$5+T8/5*Weights!$B$6+U8/5*Weights!$B$7+V8/5*Weights!$B$8-L8*Weights!$B$9,0))</f>
-        <v>70</v>
-      </c>
-      <c r="X8" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X8" s="10">
         <f>IF(W8&gt;=Weights!$B$12,"A",IF(W8&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y8" s="11" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="W9" s="10">
         <f>MAX(0,ROUND(Q9/5*Weights!$B$3+R9/5*Weights!$B$4+S9/5*Weights!$B$5+T9/5*Weights!$B$6+U9/5*Weights!$B$7+V9/5*Weights!$B$8-L9*Weights!$B$9,0))</f>
-        <v>68</v>
-      </c>
-      <c r="X9" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X9" s="10">
         <f>IF(W9&gt;=Weights!$B$12,"A",IF(W9&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y9" s="11" t="inlineStr">
         <is>
@@ -2076,11 +2076,11 @@
       </c>
       <c r="W10" s="10">
         <f>MAX(0,ROUND(Q10/5*Weights!$B$3+R10/5*Weights!$B$4+S10/5*Weights!$B$5+T10/5*Weights!$B$6+U10/5*Weights!$B$7+V10/5*Weights!$B$8-L10*Weights!$B$9,0))</f>
-        <v>64</v>
-      </c>
-      <c r="X10" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X10" s="10">
         <f>IF(W10&gt;=Weights!$B$12,"A",IF(W10&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y10" s="11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AD10" s="8" t="inlineStr">
         <is>
-          <t>Email inferred/unverified: kimmy@8vc.com (~76%). For enterprise clinical-data, 8VC bio team may co-fit.</t>
+          <t>Infra fit strengthens: enterprise health-data infrastructure / system-of-record is squarely 8VC's lane. Email inferred/unverified: kimmy@8vc.com (~76%). For enterprise clinical-data, 8VC bio team may co-fit.</t>
         </is>
       </c>
     </row>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="W11" s="10">
         <f>MAX(0,ROUND(Q11/5*Weights!$B$3+R11/5*Weights!$B$4+S11/5*Weights!$B$5+T11/5*Weights!$B$6+U11/5*Weights!$B$7+V11/5*Weights!$B$8-L11*Weights!$B$9,0))</f>
-        <v>66</v>
-      </c>
-      <c r="X11" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X11" s="10">
         <f>IF(W11&gt;=Weights!$B$12,"A",IF(W11&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y11" s="11" t="inlineStr">
         <is>
@@ -2348,11 +2348,11 @@
       </c>
       <c r="W12" s="10">
         <f>MAX(0,ROUND(Q12/5*Weights!$B$3+R12/5*Weights!$B$4+S12/5*Weights!$B$5+T12/5*Weights!$B$6+U12/5*Weights!$B$7+V12/5*Weights!$B$8-L12*Weights!$B$9,0))</f>
-        <v>58</v>
-      </c>
-      <c r="X12" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X12" s="10">
         <f>IF(W12&gt;=Weights!$B$12,"A",IF(W12&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y12" s="11" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>4</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>2</v>
@@ -2484,11 +2484,11 @@
       </c>
       <c r="W13" s="10">
         <f>MAX(0,ROUND(Q13/5*Weights!$B$3+R13/5*Weights!$B$4+S13/5*Weights!$B$5+T13/5*Weights!$B$6+U13/5*Weights!$B$7+V13/5*Weights!$B$8-L13*Weights!$B$9,0))</f>
-        <v>66</v>
-      </c>
-      <c r="X13" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X13" s="10">
         <f>IF(W13&gt;=Weights!$B$12,"A",IF(W13&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y13" s="11" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AA13" s="8" t="inlineStr">
         <is>
-          <t>Verify email; confirm health-software recency.</t>
+          <t>Verify email; confirm health-software recency. $5-12M checks lead a $6M seed cleanly.</t>
         </is>
       </c>
       <c r="AB13" s="7" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="W14" s="10">
         <f>MAX(0,ROUND(Q14/5*Weights!$B$3+R14/5*Weights!$B$4+S14/5*Weights!$B$5+T14/5*Weights!$B$6+U14/5*Weights!$B$7+V14/5*Weights!$B$8-L14*Weights!$B$9,0))</f>
-        <v>64</v>
-      </c>
-      <c r="X14" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X14" s="10">
         <f>IF(W14&gt;=Weights!$B$12,"A",IF(W14&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y14" s="11" t="inlineStr">
         <is>
@@ -2756,11 +2756,11 @@
       </c>
       <c r="W15" s="10">
         <f>MAX(0,ROUND(Q15/5*Weights!$B$3+R15/5*Weights!$B$4+S15/5*Weights!$B$5+T15/5*Weights!$B$6+U15/5*Weights!$B$7+V15/5*Weights!$B$8-L15*Weights!$B$9,0))</f>
-        <v>64</v>
-      </c>
-      <c r="X15" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X15" s="10">
         <f>IF(W15&gt;=Weights!$B$12,"A",IF(W15&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y15" s="11" t="inlineStr">
         <is>
@@ -2892,11 +2892,11 @@
       </c>
       <c r="W16" s="10">
         <f>MAX(0,ROUND(Q16/5*Weights!$B$3+R16/5*Weights!$B$4+S16/5*Weights!$B$5+T16/5*Weights!$B$6+U16/5*Weights!$B$7+V16/5*Weights!$B$8-L16*Weights!$B$9,0))</f>
-        <v>66</v>
-      </c>
-      <c r="X16" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X16" s="10">
         <f>IF(W16&gt;=Weights!$B$12,"A",IF(W16&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y16" s="11" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AD16" s="8" t="inlineStr">
         <is>
-          <t>Morgan Cheatham left BVP for Breyer. Email inferred/unverified: steve@bvp.com (pattern first@bvp.com).</t>
+          <t>Infra fit strengthens under the new positioning: system-of-record / vertical-SaaS is core BVP thesis. Morgan Cheatham left BVP for Breyer. Email inferred/unverified: steve@bvp.com (pattern first@bvp.com).</t>
         </is>
       </c>
     </row>
@@ -3028,11 +3028,11 @@
       </c>
       <c r="W17" s="10">
         <f>MAX(0,ROUND(Q17/5*Weights!$B$3+R17/5*Weights!$B$4+S17/5*Weights!$B$5+T17/5*Weights!$B$6+U17/5*Weights!$B$7+V17/5*Weights!$B$8-L17*Weights!$B$9,0))</f>
-        <v>58</v>
-      </c>
-      <c r="X17" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X17" s="10">
         <f>IF(W17&gt;=Weights!$B$12,"A",IF(W17&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y17" s="11" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>5</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>1</v>
@@ -3164,11 +3164,11 @@
       </c>
       <c r="W18" s="10">
         <f>MAX(0,ROUND(Q18/5*Weights!$B$3+R18/5*Weights!$B$4+S18/5*Weights!$B$5+T18/5*Weights!$B$6+U18/5*Weights!$B$7+V18/5*Weights!$B$8-L18*Weights!$B$9,0))</f>
-        <v>78</v>
-      </c>
-      <c r="X18" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X18" s="10">
         <f>IF(W18&gt;=Weights!$B$12,"A",IF(W18&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y18" s="11" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AD18" s="8" t="inlineStr">
         <is>
-          <t>Verified. Only functional inbox embed@conviction.com is confirmed; sarah@conviction.com / mike@conviction.com are inferred, LOW confidence. Mike Vernal (ex-Sequoia, PLG/infra) is a strong alt contact for the iViz self-serve angle.</t>
+          <t>Verified. Check 5: $1M-$25M range comfortably leads a $6M seed. Infra angle fits (Vernal = PLG/infra). Only functional inbox embed@conviction.com is confirmed; sarah@conviction.com / mike@conviction.com inferred, LOW confidence.</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="W19" s="10">
         <f>MAX(0,ROUND(Q19/5*Weights!$B$3+R19/5*Weights!$B$4+S19/5*Weights!$B$5+T19/5*Weights!$B$6+U19/5*Weights!$B$7+V19/5*Weights!$B$8-L19*Weights!$B$9,0))</f>
-        <v>53</v>
-      </c>
-      <c r="X19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X19" s="10">
         <f>IF(W19&gt;=Weights!$B$12,"A",IF(W19&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y19" s="11" t="inlineStr">
         <is>
@@ -3436,11 +3436,11 @@
       </c>
       <c r="W20" s="10">
         <f>MAX(0,ROUND(Q20/5*Weights!$B$3+R20/5*Weights!$B$4+S20/5*Weights!$B$5+T20/5*Weights!$B$6+U20/5*Weights!$B$7+V20/5*Weights!$B$8-L20*Weights!$B$9,0))</f>
-        <v>80</v>
-      </c>
-      <c r="X20" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X20" s="10">
         <f>IF(W20&gt;=Weights!$B$12,"A",IF(W20&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y20" s="11" t="inlineStr">
         <is>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="W21" s="10">
         <f>MAX(0,ROUND(Q21/5*Weights!$B$3+R21/5*Weights!$B$4+S21/5*Weights!$B$5+T21/5*Weights!$B$6+U21/5*Weights!$B$7+V21/5*Weights!$B$8-L21*Weights!$B$9,0))</f>
-        <v>44</v>
-      </c>
-      <c r="X21" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X21" s="10">
         <f>IF(W21&gt;=Weights!$B$12,"A",IF(W21&gt;=Weights!$B$13,"B","C"))</f>
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y21" s="11" t="inlineStr">
         <is>
@@ -3708,11 +3708,11 @@
       </c>
       <c r="W22" s="10">
         <f>MAX(0,ROUND(Q22/5*Weights!$B$3+R22/5*Weights!$B$4+S22/5*Weights!$B$5+T22/5*Weights!$B$6+U22/5*Weights!$B$7+V22/5*Weights!$B$8-L22*Weights!$B$9,0))</f>
-        <v>24</v>
-      </c>
-      <c r="X22" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X22" s="10">
         <f>IF(W22&gt;=Weights!$B$12,"A",IF(W22&gt;=Weights!$B$13,"B","C"))</f>
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y22" s="11" t="inlineStr">
         <is>
@@ -3844,11 +3844,11 @@
       </c>
       <c r="W23" s="10">
         <f>MAX(0,ROUND(Q23/5*Weights!$B$3+R23/5*Weights!$B$4+S23/5*Weights!$B$5+T23/5*Weights!$B$6+U23/5*Weights!$B$7+V23/5*Weights!$B$8-L23*Weights!$B$9,0))</f>
-        <v>66</v>
-      </c>
-      <c r="X23" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X23" s="10">
         <f>IF(W23&gt;=Weights!$B$12,"A",IF(W23&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y23" s="11" t="inlineStr">
         <is>
@@ -3980,11 +3980,11 @@
       </c>
       <c r="W24" s="10">
         <f>MAX(0,ROUND(Q24/5*Weights!$B$3+R24/5*Weights!$B$4+S24/5*Weights!$B$5+T24/5*Weights!$B$6+U24/5*Weights!$B$7+V24/5*Weights!$B$8-L24*Weights!$B$9,0))</f>
-        <v>60</v>
-      </c>
-      <c r="X24" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X24" s="10">
         <f>IF(W24&gt;=Weights!$B$12,"A",IF(W24&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y24" s="11" t="inlineStr">
         <is>
@@ -4116,11 +4116,11 @@
       </c>
       <c r="W25" s="10">
         <f>MAX(0,ROUND(Q25/5*Weights!$B$3+R25/5*Weights!$B$4+S25/5*Weights!$B$5+T25/5*Weights!$B$6+U25/5*Weights!$B$7+V25/5*Weights!$B$8-L25*Weights!$B$9,0))</f>
-        <v>60</v>
-      </c>
-      <c r="X25" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X25" s="10">
         <f>IF(W25&gt;=Weights!$B$12,"A",IF(W25&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y25" s="11" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="W26" s="10">
         <f>MAX(0,ROUND(Q26/5*Weights!$B$3+R26/5*Weights!$B$4+S26/5*Weights!$B$5+T26/5*Weights!$B$6+U26/5*Weights!$B$7+V26/5*Weights!$B$8-L26*Weights!$B$9,0))</f>
-        <v>58</v>
-      </c>
-      <c r="X26" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X26" s="10">
         <f>IF(W26&gt;=Weights!$B$12,"A",IF(W26&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y26" s="11" t="inlineStr">
         <is>
@@ -4388,11 +4388,11 @@
       </c>
       <c r="W27" s="10">
         <f>MAX(0,ROUND(Q27/5*Weights!$B$3+R27/5*Weights!$B$4+S27/5*Weights!$B$5+T27/5*Weights!$B$6+U27/5*Weights!$B$7+V27/5*Weights!$B$8-L27*Weights!$B$9,0))</f>
-        <v>74</v>
-      </c>
-      <c r="X27" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X27" s="10">
         <f>IF(W27&gt;=Weights!$B$12,"A",IF(W27&gt;=Weights!$B$13,"B","C"))</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="Y27" s="11" t="inlineStr">
         <is>
@@ -4524,11 +4524,11 @@
       </c>
       <c r="W28" s="10">
         <f>MAX(0,ROUND(Q28/5*Weights!$B$3+R28/5*Weights!$B$4+S28/5*Weights!$B$5+T28/5*Weights!$B$6+U28/5*Weights!$B$7+V28/5*Weights!$B$8-L28*Weights!$B$9,0))</f>
-        <v>54</v>
-      </c>
-      <c r="X28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X28" s="10">
         <f>IF(W28&gt;=Weights!$B$12,"A",IF(W28&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y28" s="11" t="inlineStr">
         <is>
@@ -4660,11 +4660,11 @@
       </c>
       <c r="W29" s="10">
         <f>MAX(0,ROUND(Q29/5*Weights!$B$3+R29/5*Weights!$B$4+S29/5*Weights!$B$5+T29/5*Weights!$B$6+U29/5*Weights!$B$7+V29/5*Weights!$B$8-L29*Weights!$B$9,0))</f>
-        <v>54</v>
-      </c>
-      <c r="X29" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X29" s="10">
         <f>IF(W29&gt;=Weights!$B$12,"A",IF(W29&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y29" s="11" t="inlineStr">
         <is>
@@ -4796,11 +4796,11 @@
       </c>
       <c r="W30" s="10">
         <f>MAX(0,ROUND(Q30/5*Weights!$B$3+R30/5*Weights!$B$4+S30/5*Weights!$B$5+T30/5*Weights!$B$6+U30/5*Weights!$B$7+V30/5*Weights!$B$8-L30*Weights!$B$9,0))</f>
-        <v>52</v>
-      </c>
-      <c r="X30" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X30" s="10">
         <f>IF(W30&gt;=Weights!$B$12,"A",IF(W30&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y30" s="11" t="inlineStr">
         <is>
@@ -4932,11 +4932,11 @@
       </c>
       <c r="W31" s="10">
         <f>MAX(0,ROUND(Q31/5*Weights!$B$3+R31/5*Weights!$B$4+S31/5*Weights!$B$5+T31/5*Weights!$B$6+U31/5*Weights!$B$7+V31/5*Weights!$B$8-L31*Weights!$B$9,0))</f>
-        <v>64</v>
-      </c>
-      <c r="X31" s="10" t="str">
+        <v/>
+      </c>
+      <c r="X31" s="10">
         <f>IF(W31&gt;=Weights!$B$12,"A",IF(W31&gt;=Weights!$B$13,"B","C"))</f>
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y31" s="11" t="inlineStr">
         <is>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -988,11 +988,11 @@
       </c>
       <c r="W2" s="10">
         <f>MAX(0,ROUND(Q2/5*Weights!$B$3+R2/5*Weights!$B$4+S2/5*Weights!$B$5+T2/5*Weights!$B$6+U2/5*Weights!$B$7+V2/5*Weights!$B$8-L2*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X2" s="10">
+        <v>84</v>
+      </c>
+      <c r="X2" s="10" t="str">
         <f>IF(W2&gt;=Weights!$B$12,"A",IF(W2&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y2" s="11" t="inlineStr">
         <is>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="W3" s="10">
         <f>MAX(0,ROUND(Q3/5*Weights!$B$3+R3/5*Weights!$B$4+S3/5*Weights!$B$5+T3/5*Weights!$B$6+U3/5*Weights!$B$7+V3/5*Weights!$B$8-L3*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X3" s="10">
+        <v>84</v>
+      </c>
+      <c r="X3" s="10" t="str">
         <f>IF(W3&gt;=Weights!$B$12,"A",IF(W3&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y3" s="11" t="inlineStr">
         <is>
@@ -1260,11 +1260,11 @@
       </c>
       <c r="W4" s="10">
         <f>MAX(0,ROUND(Q4/5*Weights!$B$3+R4/5*Weights!$B$4+S4/5*Weights!$B$5+T4/5*Weights!$B$6+U4/5*Weights!$B$7+V4/5*Weights!$B$8-L4*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X4" s="10">
+        <v>74</v>
+      </c>
+      <c r="X4" s="10" t="str">
         <f>IF(W4&gt;=Weights!$B$12,"A",IF(W4&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y4" s="11" t="inlineStr">
         <is>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="W5" s="10">
         <f>MAX(0,ROUND(Q5/5*Weights!$B$3+R5/5*Weights!$B$4+S5/5*Weights!$B$5+T5/5*Weights!$B$6+U5/5*Weights!$B$7+V5/5*Weights!$B$8-L5*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X5" s="10">
+        <v>80</v>
+      </c>
+      <c r="X5" s="10" t="str">
         <f>IF(W5&gt;=Weights!$B$12,"A",IF(W5&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y5" s="11" t="inlineStr">
         <is>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="W6" s="10">
         <f>MAX(0,ROUND(Q6/5*Weights!$B$3+R6/5*Weights!$B$4+S6/5*Weights!$B$5+T6/5*Weights!$B$6+U6/5*Weights!$B$7+V6/5*Weights!$B$8-L6*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X6" s="10">
+        <v>72</v>
+      </c>
+      <c r="X6" s="10" t="str">
         <f>IF(W6&gt;=Weights!$B$12,"A",IF(W6&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y6" s="11" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="W7" s="10">
         <f>MAX(0,ROUND(Q7/5*Weights!$B$3+R7/5*Weights!$B$4+S7/5*Weights!$B$5+T7/5*Weights!$B$6+U7/5*Weights!$B$7+V7/5*Weights!$B$8-L7*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X7" s="10">
+        <v>72</v>
+      </c>
+      <c r="X7" s="10" t="str">
         <f>IF(W7&gt;=Weights!$B$12,"A",IF(W7&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y7" s="11" t="inlineStr">
         <is>
@@ -1804,11 +1804,11 @@
       </c>
       <c r="W8" s="10">
         <f>MAX(0,ROUND(Q8/5*Weights!$B$3+R8/5*Weights!$B$4+S8/5*Weights!$B$5+T8/5*Weights!$B$6+U8/5*Weights!$B$7+V8/5*Weights!$B$8-L8*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X8" s="10">
+        <v>70</v>
+      </c>
+      <c r="X8" s="10" t="str">
         <f>IF(W8&gt;=Weights!$B$12,"A",IF(W8&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y8" s="11" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="W9" s="10">
         <f>MAX(0,ROUND(Q9/5*Weights!$B$3+R9/5*Weights!$B$4+S9/5*Weights!$B$5+T9/5*Weights!$B$6+U9/5*Weights!$B$7+V9/5*Weights!$B$8-L9*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X9" s="10">
+        <v>68</v>
+      </c>
+      <c r="X9" s="10" t="str">
         <f>IF(W9&gt;=Weights!$B$12,"A",IF(W9&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y9" s="11" t="inlineStr">
         <is>
@@ -2076,11 +2076,11 @@
       </c>
       <c r="W10" s="10">
         <f>MAX(0,ROUND(Q10/5*Weights!$B$3+R10/5*Weights!$B$4+S10/5*Weights!$B$5+T10/5*Weights!$B$6+U10/5*Weights!$B$7+V10/5*Weights!$B$8-L10*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X10" s="10">
+        <v>64</v>
+      </c>
+      <c r="X10" s="10" t="str">
         <f>IF(W10&gt;=Weights!$B$12,"A",IF(W10&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y10" s="11" t="inlineStr">
         <is>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="W11" s="10">
         <f>MAX(0,ROUND(Q11/5*Weights!$B$3+R11/5*Weights!$B$4+S11/5*Weights!$B$5+T11/5*Weights!$B$6+U11/5*Weights!$B$7+V11/5*Weights!$B$8-L11*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X11" s="10">
+        <v>66</v>
+      </c>
+      <c r="X11" s="10" t="str">
         <f>IF(W11&gt;=Weights!$B$12,"A",IF(W11&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y11" s="11" t="inlineStr">
         <is>
@@ -2348,11 +2348,11 @@
       </c>
       <c r="W12" s="10">
         <f>MAX(0,ROUND(Q12/5*Weights!$B$3+R12/5*Weights!$B$4+S12/5*Weights!$B$5+T12/5*Weights!$B$6+U12/5*Weights!$B$7+V12/5*Weights!$B$8-L12*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X12" s="10">
+        <v>58</v>
+      </c>
+      <c r="X12" s="10" t="str">
         <f>IF(W12&gt;=Weights!$B$12,"A",IF(W12&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y12" s="11" t="inlineStr">
         <is>
@@ -2484,11 +2484,11 @@
       </c>
       <c r="W13" s="10">
         <f>MAX(0,ROUND(Q13/5*Weights!$B$3+R13/5*Weights!$B$4+S13/5*Weights!$B$5+T13/5*Weights!$B$6+U13/5*Weights!$B$7+V13/5*Weights!$B$8-L13*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X13" s="10">
+        <v>70</v>
+      </c>
+      <c r="X13" s="10" t="str">
         <f>IF(W13&gt;=Weights!$B$12,"A",IF(W13&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y13" s="11" t="inlineStr">
         <is>
@@ -2620,11 +2620,11 @@
       </c>
       <c r="W14" s="10">
         <f>MAX(0,ROUND(Q14/5*Weights!$B$3+R14/5*Weights!$B$4+S14/5*Weights!$B$5+T14/5*Weights!$B$6+U14/5*Weights!$B$7+V14/5*Weights!$B$8-L14*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X14" s="10">
+        <v>64</v>
+      </c>
+      <c r="X14" s="10" t="str">
         <f>IF(W14&gt;=Weights!$B$12,"A",IF(W14&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y14" s="11" t="inlineStr">
         <is>
@@ -2756,11 +2756,11 @@
       </c>
       <c r="W15" s="10">
         <f>MAX(0,ROUND(Q15/5*Weights!$B$3+R15/5*Weights!$B$4+S15/5*Weights!$B$5+T15/5*Weights!$B$6+U15/5*Weights!$B$7+V15/5*Weights!$B$8-L15*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X15" s="10">
+        <v>64</v>
+      </c>
+      <c r="X15" s="10" t="str">
         <f>IF(W15&gt;=Weights!$B$12,"A",IF(W15&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y15" s="11" t="inlineStr">
         <is>
@@ -2892,11 +2892,11 @@
       </c>
       <c r="W16" s="10">
         <f>MAX(0,ROUND(Q16/5*Weights!$B$3+R16/5*Weights!$B$4+S16/5*Weights!$B$5+T16/5*Weights!$B$6+U16/5*Weights!$B$7+V16/5*Weights!$B$8-L16*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X16" s="10">
+        <v>66</v>
+      </c>
+      <c r="X16" s="10" t="str">
         <f>IF(W16&gt;=Weights!$B$12,"A",IF(W16&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y16" s="11" t="inlineStr">
         <is>
@@ -3028,11 +3028,11 @@
       </c>
       <c r="W17" s="10">
         <f>MAX(0,ROUND(Q17/5*Weights!$B$3+R17/5*Weights!$B$4+S17/5*Weights!$B$5+T17/5*Weights!$B$6+U17/5*Weights!$B$7+V17/5*Weights!$B$8-L17*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X17" s="10">
+        <v>58</v>
+      </c>
+      <c r="X17" s="10" t="str">
         <f>IF(W17&gt;=Weights!$B$12,"A",IF(W17&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y17" s="11" t="inlineStr">
         <is>
@@ -3164,11 +3164,11 @@
       </c>
       <c r="W18" s="10">
         <f>MAX(0,ROUND(Q18/5*Weights!$B$3+R18/5*Weights!$B$4+S18/5*Weights!$B$5+T18/5*Weights!$B$6+U18/5*Weights!$B$7+V18/5*Weights!$B$8-L18*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X18" s="10">
+        <v>80</v>
+      </c>
+      <c r="X18" s="10" t="str">
         <f>IF(W18&gt;=Weights!$B$12,"A",IF(W18&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y18" s="11" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="W19" s="10">
         <f>MAX(0,ROUND(Q19/5*Weights!$B$3+R19/5*Weights!$B$4+S19/5*Weights!$B$5+T19/5*Weights!$B$6+U19/5*Weights!$B$7+V19/5*Weights!$B$8-L19*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X19" s="10">
+        <v>53</v>
+      </c>
+      <c r="X19" s="10" t="str">
         <f>IF(W19&gt;=Weights!$B$12,"A",IF(W19&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y19" s="11" t="inlineStr">
         <is>
@@ -3436,11 +3436,11 @@
       </c>
       <c r="W20" s="10">
         <f>MAX(0,ROUND(Q20/5*Weights!$B$3+R20/5*Weights!$B$4+S20/5*Weights!$B$5+T20/5*Weights!$B$6+U20/5*Weights!$B$7+V20/5*Weights!$B$8-L20*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X20" s="10">
+        <v>80</v>
+      </c>
+      <c r="X20" s="10" t="str">
         <f>IF(W20&gt;=Weights!$B$12,"A",IF(W20&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y20" s="11" t="inlineStr">
         <is>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="W21" s="10">
         <f>MAX(0,ROUND(Q21/5*Weights!$B$3+R21/5*Weights!$B$4+S21/5*Weights!$B$5+T21/5*Weights!$B$6+U21/5*Weights!$B$7+V21/5*Weights!$B$8-L21*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X21" s="10">
+        <v>44</v>
+      </c>
+      <c r="X21" s="10" t="str">
         <f>IF(W21&gt;=Weights!$B$12,"A",IF(W21&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>C</v>
       </c>
       <c r="Y21" s="11" t="inlineStr">
         <is>
@@ -3708,11 +3708,11 @@
       </c>
       <c r="W22" s="10">
         <f>MAX(0,ROUND(Q22/5*Weights!$B$3+R22/5*Weights!$B$4+S22/5*Weights!$B$5+T22/5*Weights!$B$6+U22/5*Weights!$B$7+V22/5*Weights!$B$8-L22*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X22" s="10">
+        <v>24</v>
+      </c>
+      <c r="X22" s="10" t="str">
         <f>IF(W22&gt;=Weights!$B$12,"A",IF(W22&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>C</v>
       </c>
       <c r="Y22" s="11" t="inlineStr">
         <is>
@@ -3844,11 +3844,11 @@
       </c>
       <c r="W23" s="10">
         <f>MAX(0,ROUND(Q23/5*Weights!$B$3+R23/5*Weights!$B$4+S23/5*Weights!$B$5+T23/5*Weights!$B$6+U23/5*Weights!$B$7+V23/5*Weights!$B$8-L23*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X23" s="10">
+        <v>66</v>
+      </c>
+      <c r="X23" s="10" t="str">
         <f>IF(W23&gt;=Weights!$B$12,"A",IF(W23&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y23" s="11" t="inlineStr">
         <is>
@@ -3980,11 +3980,11 @@
       </c>
       <c r="W24" s="10">
         <f>MAX(0,ROUND(Q24/5*Weights!$B$3+R24/5*Weights!$B$4+S24/5*Weights!$B$5+T24/5*Weights!$B$6+U24/5*Weights!$B$7+V24/5*Weights!$B$8-L24*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X24" s="10">
+        <v>60</v>
+      </c>
+      <c r="X24" s="10" t="str">
         <f>IF(W24&gt;=Weights!$B$12,"A",IF(W24&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y24" s="11" t="inlineStr">
         <is>
@@ -4116,11 +4116,11 @@
       </c>
       <c r="W25" s="10">
         <f>MAX(0,ROUND(Q25/5*Weights!$B$3+R25/5*Weights!$B$4+S25/5*Weights!$B$5+T25/5*Weights!$B$6+U25/5*Weights!$B$7+V25/5*Weights!$B$8-L25*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X25" s="10">
+        <v>60</v>
+      </c>
+      <c r="X25" s="10" t="str">
         <f>IF(W25&gt;=Weights!$B$12,"A",IF(W25&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y25" s="11" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="W26" s="10">
         <f>MAX(0,ROUND(Q26/5*Weights!$B$3+R26/5*Weights!$B$4+S26/5*Weights!$B$5+T26/5*Weights!$B$6+U26/5*Weights!$B$7+V26/5*Weights!$B$8-L26*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X26" s="10">
+        <v>58</v>
+      </c>
+      <c r="X26" s="10" t="str">
         <f>IF(W26&gt;=Weights!$B$12,"A",IF(W26&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y26" s="11" t="inlineStr">
         <is>
@@ -4388,11 +4388,11 @@
       </c>
       <c r="W27" s="10">
         <f>MAX(0,ROUND(Q27/5*Weights!$B$3+R27/5*Weights!$B$4+S27/5*Weights!$B$5+T27/5*Weights!$B$6+U27/5*Weights!$B$7+V27/5*Weights!$B$8-L27*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X27" s="10">
+        <v>74</v>
+      </c>
+      <c r="X27" s="10" t="str">
         <f>IF(W27&gt;=Weights!$B$12,"A",IF(W27&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="Y27" s="11" t="inlineStr">
         <is>
@@ -4524,11 +4524,11 @@
       </c>
       <c r="W28" s="10">
         <f>MAX(0,ROUND(Q28/5*Weights!$B$3+R28/5*Weights!$B$4+S28/5*Weights!$B$5+T28/5*Weights!$B$6+U28/5*Weights!$B$7+V28/5*Weights!$B$8-L28*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X28" s="10">
+        <v>54</v>
+      </c>
+      <c r="X28" s="10" t="str">
         <f>IF(W28&gt;=Weights!$B$12,"A",IF(W28&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y28" s="11" t="inlineStr">
         <is>
@@ -4660,11 +4660,11 @@
       </c>
       <c r="W29" s="10">
         <f>MAX(0,ROUND(Q29/5*Weights!$B$3+R29/5*Weights!$B$4+S29/5*Weights!$B$5+T29/5*Weights!$B$6+U29/5*Weights!$B$7+V29/5*Weights!$B$8-L29*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X29" s="10">
+        <v>54</v>
+      </c>
+      <c r="X29" s="10" t="str">
         <f>IF(W29&gt;=Weights!$B$12,"A",IF(W29&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y29" s="11" t="inlineStr">
         <is>
@@ -4796,11 +4796,11 @@
       </c>
       <c r="W30" s="10">
         <f>MAX(0,ROUND(Q30/5*Weights!$B$3+R30/5*Weights!$B$4+S30/5*Weights!$B$5+T30/5*Weights!$B$6+U30/5*Weights!$B$7+V30/5*Weights!$B$8-L30*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X30" s="10">
+        <v>52</v>
+      </c>
+      <c r="X30" s="10" t="str">
         <f>IF(W30&gt;=Weights!$B$12,"A",IF(W30&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y30" s="11" t="inlineStr">
         <is>
@@ -4932,11 +4932,11 @@
       </c>
       <c r="W31" s="10">
         <f>MAX(0,ROUND(Q31/5*Weights!$B$3+R31/5*Weights!$B$4+S31/5*Weights!$B$5+T31/5*Weights!$B$6+U31/5*Weights!$B$7+V31/5*Weights!$B$8-L31*Weights!$B$9,0))</f>
-        <v/>
-      </c>
-      <c r="X31" s="10">
+        <v>64</v>
+      </c>
+      <c r="X31" s="10" t="str">
         <f>IF(W31&gt;=Weights!$B$12,"A",IF(W31&gt;=Weights!$B$13,"B","C"))</f>
-        <v/>
+        <v>B</v>
       </c>
       <c r="Y31" s="11" t="inlineStr">
         <is>
@@ -4969,9 +4969,3137 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Artis Ventures (AV)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>TechBio early-stage VC</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>TechBio II, $200M</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Seed to Series B; leads</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>TechBio-native (coined the term); Freenome, Stemcentrx, Cartography Biosciences.</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Thesis: data/software/AI/ML to revolutionize human health; AI-native portfolio.</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>Austin Walne (or Stuart Peterson)</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>Partner (co-leads TechBio) / Managing GP</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W32" s="10">
+        <f>MAX(0,ROUND(Q32/5*Weights!$B$3+R32/5*Weights!$B$4+S32/5*Weights!$B$5+T32/5*Weights!$B$6+U32/5*Weights!$B$7+V32/5*Weights!$B$8-L32*Weights!$B$9,0))</f>
+        <v>82</v>
+      </c>
+      <c r="X32" s="10" t="str">
+        <f>IF(W32&gt;=Weights!$B$12,"A",IF(W32&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y32" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z32" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA32" s="8" t="inlineStr">
+        <is>
+          <t>Prime TechBio lead; from this list source. Verify email and a fresh 2025-26 deal.</t>
+        </is>
+      </c>
+      <c r="AB32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.av.co/news/techbio-ii-ushering-in-the-next-era-of-techbio-innovation; https://drypowdercapital.beehiiv.com/p/artis-ventures-closes-200m-fund</t>
+        </is>
+      </c>
+      <c r="AD32" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A (TechBio). contact@av.co verified; aw@av.co / sp@av.co inferred (~92% fl-initials pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2048 Ventures</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed fund (Vertical AI, Health, Bio)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY / Canada</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Fund III, $82M, closed Jan 2026</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Leads pre-seed and seed</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>$500K to $3M</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Explicit Health + Bio mandate; 80+ portfolio.</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Vertical AI core thesis; AI-native portfolio.</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>Alex Iskold (or Paul Sethi)</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; GP / Co-Founder &amp; MP</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W33" s="10">
+        <f>MAX(0,ROUND(Q33/5*Weights!$B$3+R33/5*Weights!$B$4+S33/5*Weights!$B$5+T33/5*Weights!$B$6+U33/5*Weights!$B$7+V33/5*Weights!$B$8-L33*Weights!$B$9,0))</f>
+        <v>82</v>
+      </c>
+      <c r="X33" s="10" t="str">
+        <f>IF(W33&gt;=Weights!$B$12,"A",IF(W33&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y33" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z33" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA33" s="8" t="inlineStr">
+        <is>
+          <t>Strong seed-lead fit; fresh fund. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.2048.vc/blog/2048-ventures-raises-67m-fund-ii-to-lead-pre-seed-rounds-across-us-and-canada; https://2048.vc/team</t>
+        </is>
+      </c>
+      <c r="AD33" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A+B. alex@2048.vc Verified (pattern first@2048.vc). $500K-$3M fits as co-lead on a $6M seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Modi Ventures</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>TechBio seed/early fund (AI x biology)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Fund II, $88M, closed summer 2025 (~$134M AUM)</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Early-stage; leads/co-leads</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Yes/co</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>AI x biology 'biostack'; Generate:Biomedicines, Atomic AI, Lila Sciences, Latus Bio, Flagship ties.</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>AI x biology convergence thesis; AI-native portfolio.</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>AI drug-discovery platforms (Generate, Atomic AI, Lila) are adjacent, not competing.</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>Sahir Ali, PhD</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; General Partner</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W34" s="10">
+        <f>MAX(0,ROUND(Q34/5*Weights!$B$3+R34/5*Weights!$B$4+S34/5*Weights!$B$5+T34/5*Weights!$B$6+U34/5*Weights!$B$7+V34/5*Weights!$B$8-L34*Weights!$B$9,0))</f>
+        <v>78</v>
+      </c>
+      <c r="X34" s="10" t="str">
+        <f>IF(W34&gt;=Weights!$B$12,"A",IF(W34&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y34" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z34" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA34" s="8" t="inlineStr">
+        <is>
+          <t>Prime AI x biology lead/co-lead; fresh fund. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC34" s="8" t="inlineStr">
+        <is>
+          <t>https://vcwire.tech/2025/07/18/modi-ventures-closes-second-fund-at-88m/; https://www.modivc.com/about-us</t>
+        </is>
+      </c>
+      <c r="AD34" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A. info@modivc.com verified; sahir@modivc.com inferred. AI-drug-discovery holdings adjacent (flag, not conflict).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Coho Deeptech</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed deep-science &amp; tech fund</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Undisclosed (small independent fund)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed; leads selective early</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Selective (early)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>AI + bio/health thesis; Assort Health (healthcare AI, Mar 2025), Starling Medical (Dec 2024).</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>AI-native portfolio: Cartesia, Bland AI, Runware, AudioShake.</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>Elvis Zhang (or Jennifer Zhai)</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>Founder / Partner</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W35" s="10">
+        <f>MAX(0,ROUND(Q35/5*Weights!$B$3+R35/5*Weights!$B$4+S35/5*Weights!$B$5+T35/5*Weights!$B$6+U35/5*Weights!$B$7+V35/5*Weights!$B$8-L35*Weights!$B$9,0))</f>
+        <v>66</v>
+      </c>
+      <c r="X35" s="10" t="str">
+        <f>IF(W35&gt;=Weights!$B$12,"A",IF(W35&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y35" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z35" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA35" s="8" t="inlineStr">
+        <is>
+          <t>High-conviction early check; too small to lead a full $6M alone. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cohovc.com/; https://tracxn.com/d/venture-capital/coho/__M93dJlKqyG7YR1R9JEguYPwAoyrwT9UDeapYtK2mALc</t>
+        </is>
+      </c>
+      <c r="AD35" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A+B. partners@cohovc.com verified; first@cohovc.com inferred. Fund size undisclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>First Star Ventures</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed deep-tech fund (computing x real-world)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Fund III closed Jun 2025 (prior ~$40M)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed; leads</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>$100K to $1M</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Yes (small)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>'Computational biotechnology' in thesis; techbio + frontier-computing portfolio.</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Frontier computing + AI; anti-SaaS-playbook, infra-leaning.</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>Millie Liu (or Drew Volpe)</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" s="10">
+        <f>MAX(0,ROUND(Q36/5*Weights!$B$3+R36/5*Weights!$B$4+S36/5*Weights!$B$5+T36/5*Weights!$B$6+U36/5*Weights!$B$7+V36/5*Weights!$B$8-L36*Weights!$B$9,0))</f>
+        <v>68</v>
+      </c>
+      <c r="X36" s="10" t="str">
+        <f>IF(W36&gt;=Weights!$B$12,"A",IF(W36&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y36" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z36" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA36" s="8" t="inlineStr">
+        <is>
+          <t>Early anchor/co-lead; check too small to lead a $6M alone. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.vcsheet.com/fund/first-star-ventures; https://startupintros.com/orgs/first-star-ventures</t>
+        </is>
+      </c>
+      <c r="AD36" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A+B. millie@firststar.vc likely (pattern first@firststar.vc). $100K-$1M checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Asset Management Ventures (AMV)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Early-stage VC (digital health, tech, life sciences)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Fund V, $150M (2020)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Seed and Series A; leads</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Digital health + life sciences; Autonomize (AI, Jun 2025), Outcomes4Me.</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Some AI (Autonomize); not an AI-first fund.</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>Skip Fleshman (or Lou Lange)</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P37" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W37" s="10">
+        <f>MAX(0,ROUND(Q37/5*Weights!$B$3+R37/5*Weights!$B$4+S37/5*Weights!$B$5+T37/5*Weights!$B$6+U37/5*Weights!$B$7+V37/5*Weights!$B$8-L37*Weights!$B$9,0))</f>
+        <v>60</v>
+      </c>
+      <c r="X37" s="10" t="str">
+        <f>IF(W37&gt;=Weights!$B$12,"A",IF(W37&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y37" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z37" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA37" s="8" t="inlineStr">
+        <is>
+          <t>Plausible seed lead/co-lead; low deal cadence, selective. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC37" s="8" t="inlineStr">
+        <is>
+          <t>https://assetman.com/; https://theorg.com/org/asset-management-ventures-amv</t>
+        </is>
+      </c>
+      <c r="AD37" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A+B. Email pattern unconfirmed (first@assetman.com inferred). Fund V 2020 is aging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>1984 Ventures</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Seed vertical-software fund</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Undisclosed (active seed fund)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Leads first (seed) rounds</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Up to ~$1M lead</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Yes (small check)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Digital-health lane: software that expands capacity inside clinical systems (on-message).</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Vertical AI + developer tools &amp; infrastructure core thesis.</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (verify partner)</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" s="10">
+        <f>MAX(0,ROUND(Q38/5*Weights!$B$3+R38/5*Weights!$B$4+S38/5*Weights!$B$5+T38/5*Weights!$B$6+U38/5*Weights!$B$7+V38/5*Weights!$B$8-L38*Weights!$B$9,0))</f>
+        <v>68</v>
+      </c>
+      <c r="X38" s="10" t="str">
+        <f>IF(W38&gt;=Weights!$B$12,"A",IF(W38&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y38" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z38" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA38" s="8" t="inlineStr">
+        <is>
+          <t>On-message (vertical AI + dev-infra + clinical workflow); small lead check. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC38" s="8" t="inlineStr">
+        <is>
+          <t>https://1984.vc/; https://www.vcsheet.com/fund/1984-ventures</t>
+        </is>
+      </c>
+      <c r="AD38" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door B+C. Partner name + recent deal unverified this pass. Email pattern Unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Starbloom Capital</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Early-stage deep-tech fund (longevity bio, neuroAI)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY / SF</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Seed and Series A; leads</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>$250K to $5M</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Longevity biotech + neuro; Adaptyx Biosciences $14M seed (Oct 2025), Inventex (Apr 2025).</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>NeuroAI + AI thesis.</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>James Fickel</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Director</t>
+        </is>
+      </c>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W39" s="10">
+        <f>MAX(0,ROUND(Q39/5*Weights!$B$3+R39/5*Weights!$B$4+S39/5*Weights!$B$5+T39/5*Weights!$B$6+U39/5*Weights!$B$7+V39/5*Weights!$B$8-L39*Weights!$B$9,0))</f>
+        <v>66</v>
+      </c>
+      <c r="X39" s="10" t="str">
+        <f>IF(W39&gt;=Weights!$B$12,"A",IF(W39&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y39" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z39" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA39" s="8" t="inlineStr">
+        <is>
+          <t>Thesis-adjacent (longevity/neuroAI); possible seed participant/co-lead. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.starbloom.capital/; https://superscout.co/investor/starbloom-capital</t>
+        </is>
+      </c>
+      <c r="AD39" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A/B. james@starbloom.capital inferred (ZoomInfo j***). Fund size undisclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Qiming Venture Partners USA</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare VC (US arm)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Cambridge, MA / Palo Alto</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>US Healthcare Fund III, $260M (2022)</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Seed to Series B; selective at seed</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare fund, therapeutics-weighted; 'healthcare technology' mandate in Fund III.</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Limited AI-software evidence.</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>Isaac Ciechanover, MD</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>US Partner</t>
+        </is>
+      </c>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" s="10">
+        <f>MAX(0,ROUND(Q40/5*Weights!$B$3+R40/5*Weights!$B$4+S40/5*Weights!$B$5+T40/5*Weights!$B$6+U40/5*Weights!$B$7+V40/5*Weights!$B$8-L40*Weights!$B$9,0))</f>
+        <v>52</v>
+      </c>
+      <c r="X40" s="10" t="str">
+        <f>IF(W40&gt;=Weights!$B$12,"A",IF(W40&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y40" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z40" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA40" s="8" t="inlineStr">
+        <is>
+          <t>Therapeutics-leaning; needs the healthtech-tools angle. Team flux. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20220602005291/en/; https://www.qimingvc.com/en/team/nisa-leung</t>
+        </is>
+      </c>
+      <c r="AD40" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door A (partial). Email pattern Unknown. Nisa Leung (China head) departed Feb 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Amasia</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Early-stage software VC (climate/sustainability tilt)</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco / Singapore</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Fund III (size unconfirmed)</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Seed to Series B; leads/co-leads</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>$1M to $5M</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Software-only; no drug-dev/life-science core.</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Software VC; some AI (EvolutionIQ). Thesis skews climate/sustainability/behavior-change.</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>Ramanan Raghavendran</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W41" s="10">
+        <f>MAX(0,ROUND(Q41/5*Weights!$B$3+R41/5*Weights!$B$4+S41/5*Weights!$B$5+T41/5*Weights!$B$6+U41/5*Weights!$B$7+V41/5*Weights!$B$8-L41*Weights!$B$9,0))</f>
+        <v>50</v>
+      </c>
+      <c r="X41" s="10" t="str">
+        <f>IF(W41&gt;=Weights!$B$12,"A",IF(W41&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y41" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z41" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA41" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical software-seed fit but thematic miss (sustainability). Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.amasia.vc/team; https://www.vcsheet.com/fund/amasia</t>
+        </is>
+      </c>
+      <c r="AD41" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door B (weak). first@amasia.vc inferred. Fund III size unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Zone 2 Ventures</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed generalist (AI, healthcare, fintech)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>London (US/Delaware fund)</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Fund I opened Dec 2024 (~7 cos)</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed; likely co-invests</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>AI + healthcare in mandate; portfolio too early to cite a drug-dev holding.</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>AI in mandate; new fund.</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>Ricardo Schaefer</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>Cold; open inbound. No named node.</t>
+        </is>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" s="10">
+        <f>MAX(0,ROUND(Q42/5*Weights!$B$3+R42/5*Weights!$B$4+S42/5*Weights!$B$5+T42/5*Weights!$B$6+U42/5*Weights!$B$7+V42/5*Weights!$B$8-L42*Weights!$B$9,0))</f>
+        <v>48</v>
+      </c>
+      <c r="X42" s="10" t="str">
+        <f>IF(W42&gt;=Weights!$B$12,"A",IF(W42&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y42" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z42" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA42" s="8" t="inlineStr">
+        <is>
+          <t>Small/new fund; seed participant not lead. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC42" s="8" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/fund/29431-09F; https://app.dealroom.co/companies/zone_ii_ventures</t>
+        </is>
+      </c>
+      <c r="AD42" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door B (loose). Email Unknown. Fund I opened Dec 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Lilly Ventures</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Pharma corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>~$200M CVC</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Early-to-expansion; leads</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Selective (CVC)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Therapeutically agnostic CVC; biotech, healthcare IT, medtech.</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Insilico Medicine (AI drug discovery, Jun 2025), basys.ai; Lilly's $500M a16z AI-biotech fund (Jan 2025).</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly; note Lilly builds internal drug-dev tooling (strategic sensitivity).</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (verify partner)</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>Cold; strategic. No named node.</t>
+        </is>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" s="10">
+        <f>MAX(0,ROUND(Q43/5*Weights!$B$3+R43/5*Weights!$B$4+S43/5*Weights!$B$5+T43/5*Weights!$B$6+U43/5*Weights!$B$7+V43/5*Weights!$B$8-L43*Weights!$B$9,0))</f>
+        <v>64</v>
+      </c>
+      <c r="X43" s="10" t="str">
+        <f>IF(W43&gt;=Weights!$B$12,"A",IF(W43&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y43" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z43" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA43" s="8" t="inlineStr">
+        <is>
+          <t>Strategic CVC + potential customer; not a classic $6M seed lead. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC43" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cbinsights.com/investor/lilly-ventures; https://www.crunchbase.com/organization/lilly-ventures</t>
+        </is>
+      </c>
+      <c r="AD43" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. 'Lilly Research Laboratories' is Lilly R&amp;D, NOT an investor; the venture arm is Lilly Ventures. Door A/C strategic. CVC terms can constrain future strategic buyers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Mubadala Capital</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Sovereign-backed VC/asset manager</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Abu Dhabi / SF / London</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>~$400M ventures fund</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Primarily Series B+; selective seed</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>$10M to $50M</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>No/Selective</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Digital health among sectors; not core.</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise software / AI / fintech.</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>None competing directly with Foresight/iViz identified.</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (verify partner)</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W44" s="10">
+        <f>MAX(0,ROUND(Q44/5*Weights!$B$3+R44/5*Weights!$B$4+S44/5*Weights!$B$5+T44/5*Weights!$B$6+U44/5*Weights!$B$7+V44/5*Weights!$B$8-L44*Weights!$B$9,0))</f>
+        <v>40</v>
+      </c>
+      <c r="X44" s="10" t="str">
+        <f>IF(W44&gt;=Weights!$B$12,"A",IF(W44&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y44" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z44" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA44" s="8" t="inlineStr">
+        <is>
+          <t>Stage/check far too large for a $6M seed; revisit at Series A/B. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mubadalacapital.ae/ventures; https://www.vcsheet.com/fund/mubadala</t>
+        </is>
+      </c>
+      <c r="AD44" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. Door C in theory but $10-50M checks. Sovereign-LP sensitivities for some US customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Neovate Capital Partners</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Medtech &amp; biopharma VC</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh / Denver / New Haven</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Early-stage medical devices &amp; therapeutics</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>No (devices/therapeutics)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Neuromodulation, tissue regeneration, robotic/AI-enabled interventional devices. No software holdings.</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>AI-enabled devices only; not a software/data investor.</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>Nicholas Pachuda (or Mike Green)</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>General Partner</t>
+        </is>
+      </c>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W45" s="10">
+        <f>MAX(0,ROUND(Q45/5*Weights!$B$3+R45/5*Weights!$B$4+S45/5*Weights!$B$5+T45/5*Weights!$B$6+U45/5*Weights!$B$7+V45/5*Weights!$B$8-L45*Weights!$B$9,0))</f>
+        <v>32</v>
+      </c>
+      <c r="X45" s="10" t="str">
+        <f>IF(W45&gt;=Weights!$B$12,"A",IF(W45&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y45" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z45" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA45" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis: devices/therapeutics, not software. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC45" s="8" t="inlineStr">
+        <is>
+          <t>https://app.dealroom.co/companies/neovate_capital_partners; https://mnvc.org/speakers/neovate-capital-dr-nicholas-pachuda-general-partner/</t>
+        </is>
+      </c>
+      <c r="AD45" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT. Email Unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Epidarex Capital</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Therapeutics life-science VC</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Edinburgh / US</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV first close $145M (Jan 2026)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Early-stage; leads Series A therapeutics</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>No (therapeutics)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Apellis, Nodthera, Kynos, Lunac (drug developers). No data/software holdings.</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>None; therapeutics investor.</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W46" s="10">
+        <f>MAX(0,ROUND(Q46/5*Weights!$B$3+R46/5*Weights!$B$4+S46/5*Weights!$B$5+T46/5*Weights!$B$6+U46/5*Weights!$B$7+V46/5*Weights!$B$8-L46*Weights!$B$9,0))</f>
+        <v>36</v>
+      </c>
+      <c r="X46" s="10" t="str">
+        <f>IF(W46&gt;=Weights!$B$12,"A",IF(W46&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y46" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z46" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA46" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis therapeutics VC. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC46" s="8" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/01/27/3226083/0/en/epidarex-capital-announces-first-close-of-fund-iv-securing-145-million.html</t>
+        </is>
+      </c>
+      <c r="AD46" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT. Fresh Fund IV but drug developers only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Duke Capital Partners</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>University venture arm</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Durham, NC</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Duke Innovation Fund (angel platform)</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Early-stage; Duke-affiliated startups only</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>$500K to $2M</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>60+ Duke-network companies; no stated AI/life-science infra thesis.</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>None stated.</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W47" s="10">
+        <f>MAX(0,ROUND(Q47/5*Weights!$B$3+R47/5*Weights!$B$4+S47/5*Weights!$B$5+T47/5*Weights!$B$6+U47/5*Weights!$B$7+V47/5*Weights!$B$8-L47*Weights!$B$9,0))</f>
+        <v>34</v>
+      </c>
+      <c r="X47" s="10" t="str">
+        <f>IF(W47&gt;=Weights!$B$12,"A",IF(W47&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y47" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z47" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>Gated to Duke affiliation; only if Coharts has a Duke tie. Sourced via Jennacap.ai.</t>
+        </is>
+      </c>
+      <c r="AB47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC47" s="8" t="inlineStr">
+        <is>
+          <t>https://dukecapitalpartners.duke.edu/about/; https://massinvestordatabase.com/publicfirm.php?name=Duke+Capital+Partners</t>
+        </is>
+      </c>
+      <c r="AD47" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT unless Duke-affiliated. $500K-$2M checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Lifespan Vision Ventures</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Longevity-biotech therapeutics VC</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Norwalk, CT / SF / London</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Undisclosed</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed to Series A; co-leads</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>No (therapeutics)</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Telomere/senolytics/mRNA/regenerative therapeutics; co-led Sift Bio $3.7M pre-seed.</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>None; longevity therapeutics.</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>Andrew Worden</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W48" s="10">
+        <f>MAX(0,ROUND(Q48/5*Weights!$B$3+R48/5*Weights!$B$4+S48/5*Weights!$B$5+T48/5*Weights!$B$6+U48/5*Weights!$B$7+V48/5*Weights!$B$8-L48*Weights!$B$9,0))</f>
+        <v>36</v>
+      </c>
+      <c r="X48" s="10" t="str">
+        <f>IF(W48&gt;=Weights!$B$12,"A",IF(W48&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y48" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z48" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis longevity therapeutics. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC48" s="8" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/lifespan-vision-ventures-co-leads-170000649.html</t>
+        </is>
+      </c>
+      <c r="AD48" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Criteria Bio Ventures</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Therapeutics life-science VC</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Part of CriteriaCaixa</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Leads biotech rounds (EU/NA)</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>No (therapeutics)</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Led Adaptam Therapeutics EUR3M; drug developers only.</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>None; therapeutics.</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W49" s="10">
+        <f>MAX(0,ROUND(Q49/5*Weights!$B$3+R49/5*Weights!$B$4+S49/5*Weights!$B$5+T49/5*Weights!$B$6+U49/5*Weights!$B$7+V49/5*Weights!$B$8-L49*Weights!$B$9,0))</f>
+        <v>32</v>
+      </c>
+      <c r="X49" s="10" t="str">
+        <f>IF(W49&gt;=Weights!$B$12,"A",IF(W49&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y49" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z49" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis therapeutics VC, EU-centric. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC49" s="8" t="inlineStr">
+        <is>
+          <t>https://www.criteriabioventures.com/; https://capital-riesgo.es/en/articles/criteria-bio-ventures-leads-a-3-million-investment-in-adaptam-therapeutics/</t>
+        </is>
+      </c>
+      <c r="AD49" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>NYSERDA</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>NY State clean-energy agency (government)</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Albany, NY</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>NY Green Bank / Clean Energy Fund</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Grants + co-invest, pre-Series B cleantech</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>No (cleantech grants)</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Clean-energy/cleantech only; not healthcare/software.</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (program portals)</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t>Cold; program application only.</t>
+        </is>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W50" s="10">
+        <f>MAX(0,ROUND(Q50/5*Weights!$B$3+R50/5*Weights!$B$4+S50/5*Weights!$B$5+T50/5*Weights!$B$6+U50/5*Weights!$B$7+V50/5*Weights!$B$8-L50*Weights!$B$9,0))</f>
+        <v>12</v>
+      </c>
+      <c r="X50" s="10" t="str">
+        <f>IF(W50&gt;=Weights!$B$12,"A",IF(W50&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y50" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z50" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis (cleantech, government). Exclude. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC50" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nyserda.ny.gov/All-Programs/Innovation-at-NYSERDA</t>
+        </is>
+      </c>
+      <c r="AD50" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. OFF-THESIS. Clean-energy mandate only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Perceptive Xontogeny Ventures</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Therapeutics platform (Perceptive + Xontogeny)</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>New York / Boston</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Fund II $515M (May 2021)</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Leads Series A/B; clinical-stage drugs</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>$10M to $20M</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>No (therapeutics)</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Landos (acq. AbbVie 2024), Lexeo; advancing drug products preclinical to clinical.</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>None; therapeutics.</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W51" s="10">
+        <f>MAX(0,ROUND(Q51/5*Weights!$B$3+R51/5*Weights!$B$4+S51/5*Weights!$B$5+T51/5*Weights!$B$6+U51/5*Weights!$B$7+V51/5*Weights!$B$8-L51*Weights!$B$9,0))</f>
+        <v>38</v>
+      </c>
+      <c r="X51" s="10" t="str">
+        <f>IF(W51&gt;=Weights!$B$12,"A",IF(W51&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y51" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z51" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA51" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis therapeutics; checks 2-3x the whole seed. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB51" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC51" s="8" t="inlineStr">
+        <is>
+          <t>https://xontogeny.com/news/perceptive-advisors-closes-515-million-perceptive-xontogeny-venture-fund-ii-lp/</t>
+        </is>
+      </c>
+      <c r="AD51" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT. $10-20M concentrated therapeutics checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Abingworth</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Therapeutics life-science investor (Carlyle)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>London / Boston</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Bioventures 8 ~$466M</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Seed to clinical co-development; drugs</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>No (therapeutics)</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Biotherapeutics, gene/cell therapy, small molecules; drug developers.</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>None; therapeutics.</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P52" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W52" s="10">
+        <f>MAX(0,ROUND(Q52/5*Weights!$B$3+R52/5*Weights!$B$4+S52/5*Weights!$B$5+T52/5*Weights!$B$6+U52/5*Weights!$B$7+V52/5*Weights!$B$8-L52*Weights!$B$9,0))</f>
+        <v>40</v>
+      </c>
+      <c r="X52" s="10" t="str">
+        <f>IF(W52&gt;=Weights!$B$12,"A",IF(W52&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y52" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z52" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA52" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis therapeutics investor. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB52" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC52" s="8" t="inlineStr">
+        <is>
+          <t>https://www.abingworth.com/about</t>
+        </is>
+      </c>
+      <c r="AD52" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>3M Ventures</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Industrial corporate venture arm</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>St. Paul, MN</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Corporate CVC</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Climate tech, industrial automation, materials, semiconductors</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>No (strategic)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>No life-science/software-infra thesis.</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Some AI in industrial context; off-thesis for drug-dev.</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>Cold; strategic only.</t>
+        </is>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W53" s="10">
+        <f>MAX(0,ROUND(Q53/5*Weights!$B$3+R53/5*Weights!$B$4+S53/5*Weights!$B$5+T53/5*Weights!$B$6+U53/5*Weights!$B$7+V53/5*Weights!$B$8-L53*Weights!$B$9,0))</f>
+        <v>22</v>
+      </c>
+      <c r="X53" s="10" t="str">
+        <f>IF(W53&gt;=Weights!$B$12,"A",IF(W53&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y53" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z53" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA53" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis industrial/materials/climate CVC. Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB53" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC53" s="8" t="inlineStr">
+        <is>
+          <t>https://www.3m.com/3M/en_US/about-3m/ventures/</t>
+        </is>
+      </c>
+      <c r="AD53" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT. JetZero Mar 2026, Ayar Labs Dec 2024 (aerospace/semis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>At One Ventures</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Climate/nature deep-tech VC</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>~$525M AUM</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Seed/early; climate/nature hardware</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>No (climate hardware)</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Climate/nature-positive hardware; buildings, energy, food/ag.</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Deep tech; off-thesis for drug-dev software.</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>None identified.</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>Tom Chi</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="P54" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W54" s="10">
+        <f>MAX(0,ROUND(Q54/5*Weights!$B$3+R54/5*Weights!$B$4+S54/5*Weights!$B$5+T54/5*Weights!$B$6+U54/5*Weights!$B$7+V54/5*Weights!$B$8-L54*Weights!$B$9,0))</f>
+        <v>26</v>
+      </c>
+      <c r="X54" s="10" t="str">
+        <f>IF(W54&gt;=Weights!$B$12,"A",IF(W54&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y54" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z54" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA54" s="8" t="inlineStr">
+        <is>
+          <t>Off-thesis (climate/nature hardware). Sourced via Jennacap.ai (screened out).</t>
+        </is>
+      </c>
+      <c r="AB54" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC54" s="8" t="inlineStr">
+        <is>
+          <t>https://impactalpha.com/at-one-ventures-closes-375-million-deeptech-climate-fund/</t>
+        </is>
+      </c>
+      <c r="AD54" s="8" t="inlineStr">
+        <is>
+          <t>Sourced via Jennacap.ai. POOR FIT.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD31"/>
-  <conditionalFormatting sqref="W2:W31">
+  <autoFilter ref="A1:AD54"/>
+  <conditionalFormatting sqref="W2:W54">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4984,14 +8112,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y2:Y231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not contacted,Researching,Intro requested,Intro made,First meeting,Diligence,Term sheet,Closed,Passed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q231 R2:R231 S2:S231 T2:T231 U2:U231 V2:V231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="Q2:Q254 R2:R254 S2:S254 T2:T254 U2:U254 V2:V254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -5192,7 +8320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6174,6 +9302,627 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Artis Ventures (AV)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>TechBio II $200M; leads health-AI rounds (Cartography B Oct 2025)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Dry Powder / av.co</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>https://drypowdercapital.beehiiv.com/p/artis-ventures-closes-200m-fund</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2048 Ventures</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Fund III $82M Jan 2026; leads seed; Vertical AI + Health + Bio</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>2048.vc / buildmvpfast</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.buildmvpfast.com/blog/2048vc-pre-seed-fast-track-vertical-ai-startup-funding-2026</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Modi Ventures</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Fund II $88M 2025; AI x biology; Brainomix Feb 2026, RBL Aug 2025</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>VCwire</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>https://vcwire.tech/2025/07/18/modi-ventures-closes-second-fund-at-88m/</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Coho Deeptech</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>AI + bio/health pre-seed/seed; Runware Dec 2025</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Coho / Tracxn</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cohovc.com/</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>First Star Ventures</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Fund III Jun 2025; computational biotech; Extellis $6.8M Seed Nov 2025</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>VC Sheet / StartupIntros</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.vcsheet.com/fund/first-star-ventures</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Asset Management Ventures (AMV)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Fund V $150M; Autonomize Series A Jun 2025</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Asset Management Ventures / Tracxn</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>https://assetman.com/</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>1984 Ventures</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Thesis: vertical AI, dev tools &amp; infra, digital health</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>1984.vc</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>https://1984.vc/</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Starbloom Capital</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Led Adaptyx $14M seed Oct 2025</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Starbloom / Crunchbase</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.starbloom.capital/</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Qiming Venture Partners USA</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>US Healthcare Fund III $260M 2022</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>BusinessWire / FierceBiotech</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20220602005291/en/</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Amasia</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>EvolutionIQ Series C Aug 2024; Topanga Series A Feb 2025</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Amasia / VC Sheet</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>https://www.amasia.vc/team</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Zone 2 Ventures</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Fund I opened Dec 2024; AI + healthcare mandate</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>PitchBook / Dealroom</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>https://app.dealroom.co/companies/zone_ii_ventures</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Lilly Ventures</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Backs Insilico Medicine (AI drug discovery), basys.ai</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>CB Insights</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cbinsights.com/investor/lilly-ventures</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Mubadala Capital</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>~$400M ventures fund; Series B+ growth deals (Waymo, HERE)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Mubadala Capital / VC Sheet</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mubadalacapital.ae/ventures</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Neovate Capital Partners</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Medtech &amp; biopharma (devices/therapeutics) focus</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Dealroom / MNVC</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>https://app.dealroom.co/companies/neovate_capital_partners</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Epidarex Capital</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV first close $145M Jan 2026 (therapeutics)</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/01/27/3226083/0/en/epidarex-capital-announces-first-close-of-fund-iv-securing-145-million.html</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Duke Capital Partners</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Duke-affiliated early-stage; $500K-$2M</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Duke Capital Partners</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>https://dukecapitalpartners.duke.edu/about/</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Lifespan Vision Ventures</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Co-led Sift Biosciences $3.7M pre-seed</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/lifespan-vision-ventures-co-leads-170000649.html</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Criteria Bio Ventures</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Led Adaptam Therapeutics EUR3M (therapeutics)</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Capital Riesgo</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>https://capital-riesgo.es/en/articles/criteria-bio-ventures-leads-a-3-million-investment-in-adaptam-therapeutics/</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>NYSERDA</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>NY State cleantech grants/co-investment</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>NYSERDA</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nyserda.ny.gov/All-Programs/Innovation-at-NYSERDA</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Perceptive Xontogeny Ventures</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Fund II $515M May 2021 (therapeutics)</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Xontogeny</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>https://xontogeny.com/news/perceptive-advisors-closes-515-million-perceptive-xontogeny-venture-fund-ii-lp/</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Abingworth</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Bioventures 8 ~$466M (therapeutics)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Abingworth</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>https://www.abingworth.com/about</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>3M Ventures</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Industrial/climate/materials CVC</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>3M Ventures</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.3m.com/3M/en_US/about-3m/ventures/</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>At One Ventures</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>~$525M climate/nature deep-tech AUM</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>ImpactAlpha</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>https://impactalpha.com/at-one-ventures-closes-375-million-deeptech-climate-fund/</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8097,9 +8097,417 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Oncology Ventures</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Seed-stage cancer-care data/AI fund (single-GP)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Fund I, $30M (~2024); a ~$62M 2026 figure is unconfirmed</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed cancer-care data &amp; tech; often co-invests</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Selective (co-invests often)</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Yes (CRM: lead, CONNECTED)</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Oncology-only, NON-drug: cancer-care data, AI, interoperability. Strategic LPs Cardinal Health, City of Hope, Moffitt. Does NOT fund therapeutics/devices.</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Cancer data + AI thesis; Risa/RISA Labs (AI oncology workflow, Apr 2025), Tono, Lumonus, mPATH.</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>IgniteData / Archer (EHR-to-EDC clinical-trial data transfer) is a soft adjacency to Foresight's data management, not a hard conflict.</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>Ben Freeberg</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="P55" s="8" t="inlineStr">
+        <is>
+          <t>DIRECT: existing CONNECTED relationship in the CRM with the MP (last contacted Jun 2026). Work directly, not via DLA.</t>
+        </is>
+      </c>
+      <c r="Q55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V55" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W55" s="10">
+        <f>MAX(0,ROUND(Q55/5*Weights!$B$3+R55/5*Weights!$B$4+S55/5*Weights!$B$5+T55/5*Weights!$B$6+U55/5*Weights!$B$7+V55/5*Weights!$B$8-L55*Weights!$B$9,0))</f>
+        <v>70</v>
+      </c>
+      <c r="X55" s="10" t="str">
+        <f>IF(W55&gt;=Weights!$B$12,"A",IF(W55&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y55" s="11" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="Z55" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA55" s="8" t="inlineStr">
+        <is>
+          <t>Work the existing Ben Freeberg relationship directly; front an oncology-program angle. Note co-invest tendency (line up a lead).</t>
+        </is>
+      </c>
+      <c r="AB55" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC55" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hcinnovationgroup.com/finance-revenue-cycle/news/55136523/oncology-focused-venture-capital-firm-closes-30m-fund; https://www.crunchbase.com/organization/oncology-ventures</t>
+        </is>
+      </c>
+      <c r="AD55" s="8" t="inlineStr">
+        <is>
+          <t>Already in HubSpot (lead, CONNECTED). Email ben@oncology.ventures VERIFIED via CRM contact. Warm-path 5 = direct existing relationship. Oncology-only mandate is the main fit caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Silversmith Capital Partners</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Growth-equity firm (healthcare IT / vertical SaaS)</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Fund V, $1.7B, closed Jul 2025 ($5B+ AUM)</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Growth-stage (Series B+); minority or majority</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>$20M to $125M</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>No (growth-stage)</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Deep Healthcare IT &amp; Services book: Iodine Software (clinical AI/CDI), Panalgo (RWD/HEOR), Centauri, LifeStance, Nordic.</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Vertical SaaS + information services; some AI (Iodine clinical AI). Not an AI-for-science specialist.</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Panalgo (RWD/HEOR analytics) is adjacent to iViz but exited to Norstella (no longer active); not a live conflict.</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>Jeff Crisan</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Managing Partner, Healthcare IT &amp; Services (alt: Jim Quagliaroli)</t>
+        </is>
+      </c>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>Cold; no named node.</t>
+        </is>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W56" s="10">
+        <f>MAX(0,ROUND(Q56/5*Weights!$B$3+R56/5*Weights!$B$4+S56/5*Weights!$B$5+T56/5*Weights!$B$6+U56/5*Weights!$B$7+V56/5*Weights!$B$8-L56*Weights!$B$9,0))</f>
+        <v>54</v>
+      </c>
+      <c r="X56" s="10" t="str">
+        <f>IF(W56&gt;=Weights!$B$12,"A",IF(W56&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y56" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z56" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA56" s="8" t="inlineStr">
+        <is>
+          <t>WRONG STAGE for a $6M seed ($20M+ checks). File for Series B+; keep Jeff Crisan warm.</t>
+        </is>
+      </c>
+      <c r="AB56" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC56" s="8" t="inlineStr">
+        <is>
+          <t>https://www.silversmith.com/news/silversmith-capital-partners-closes-1-7-billion-fifth-fund; https://www.silversmith.com/portfolio</t>
+        </is>
+      </c>
+      <c r="AD56" s="8" t="inlineStr">
+        <is>
+          <t>Right thesis (Door C, healthcare IT / vertical SaaS), wrong stage. Score 54 overstates seed-fit; treat as a later-round name. Email jcrisan@silversmith.com inferred (ZoomInfo j***@silversmith.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Care Equity</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Private equity (growth/control, life-science tools &amp; services)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Care Equity II, $302M (Oct 2022); Fund I $125M (~$425M AUM)</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Growth/buyout PE; NOT venture seed</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Unknown (8-figure PE checks)</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Yes (CRM: lead)</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>Wet-lab / bioanalytics tools &amp; services: OmicScouts (proteomics, exited to Momentum Mar 2025), TATAA Biocenter, Sapient Bioanalytics.</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>None found; no AI/software-infrastructure holdings.</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>None competing with Foresight/iViz; portfolio is lab services.</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>Sofia Etlin (firm: Peter Batesko, Founder/CEO)</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>CRM contact</t>
+        </is>
+      </c>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t>Existing CRM contact (Sofia Etlin, lead stage); lighter than Oncology Ventures. Work directly if pursued.</t>
+        </is>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" s="10">
+        <f>MAX(0,ROUND(Q57/5*Weights!$B$3+R57/5*Weights!$B$4+S57/5*Weights!$B$5+T57/5*Weights!$B$6+U57/5*Weights!$B$7+V57/5*Weights!$B$8-L57*Weights!$B$9,0))</f>
+        <v>42</v>
+      </c>
+      <c r="X57" s="10" t="str">
+        <f>IF(W57&gt;=Weights!$B$12,"A",IF(W57&gt;=Weights!$B$13,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="Y57" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z57" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA57" s="8" t="inlineStr">
+        <is>
+          <t>PASS: off-thesis PE (control in lab tools/services), wrong structure for a $6M software seed.</t>
+        </is>
+      </c>
+      <c r="AB57" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC57" s="8" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/investor/458093-80; https://www.privateequityinternational.com/institution-profiles/care-equity.html</t>
+        </is>
+      </c>
+      <c r="AD57" s="8" t="inlineStr">
+        <is>
+          <t>Already in HubSpot (lead). Email sofia@careequity.com VERIFIED via CRM; firm head Peter Batesko (peter@careequity.com inferred). Off-thesis growth/control PE in life-science lab services.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD54"/>
-  <conditionalFormatting sqref="W2:W54">
+  <autoFilter ref="A1:AD57"/>
+  <conditionalFormatting sqref="W2:W57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -8112,14 +8520,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y2:Y254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not contacted,Researching,Intro requested,Intro made,First meeting,Diligence,Term sheet,Closed,Passed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q254 R2:R254 S2:S254 T2:T254 U2:U254 V2:V254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="Q2:Q257 R2:R257 S2:S257 T2:T257 U2:U257 V2:V257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -8320,7 +8728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9923,6 +10331,141 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Oncology Ventures</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>$30M cancer-focused seed fund; non-drug mandate</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>HC Innovation Group</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hcinnovationgroup.com/finance-revenue-cycle/news/55136523/oncology-focused-venture-capital-firm-closes-30m-fund</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Oncology Ventures</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Ben Freeberg MP, CONNECTED contact</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>HubSpot CRM</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>HubSpot company 330285638360 / contact 508812255971</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Silversmith Capital Partners</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Fund V $1.7B Jul 2025; $20-125M checks; healthcare-IT book</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Silversmith</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.silversmith.com/news/silversmith-capital-partners-closes-1-7-billion-fifth-fund</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Care Equity</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Care Equity II $302M Oct 2022; life-science PE</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/investor/458093-80</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Care Equity</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Etlin CRM contact</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>HubSpot CRM</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>HubSpot company 348445133500 / contact 558213895894</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Institutional Seed, $6M target (valuation TBD with lead; ~26 months runway). POSITIONING UPDATE per Oct 2026 deck: Coharts = drug-development INFRASTRUCTURE, 'one record per program, from first assay to filing, with the models built in.' Foresight Base is the program record ($2K/program/month; Part 11 + ICH E6(R3) data management) with modules (PRISM, ATHENA, BEAM, CTS, iViz) switching on by stage. Applied AI, IaaS (never SaaS). Now also competes with the record/eTMF vaults (Veeva, Medidata Rave, Benchling), not only simulation tools, adding a THIRD investor door: enterprise / vertical-SaaS / dev-infrastructure. Validation is RETROSPECTIVE (LEAP Phase 2, bioavailability, failures re-run); NSCLC in PoC. Traction: Tempus POC (results for JPM Jan 2027), Synthon generics pilot complete (paid conversion $250K-$415K), PRISM with 2 pediatric hospitals (FDA grant filed/pending). A $6M seed favors seed-LEADING funds; most check sizes Unknown pending PitchBook; personal emails inferred unless marked Verified. None of these firms are in the HubSpot pipeline. CONFLICT FLAGGED: Radical Ventures holds Unlearn.AI (direct competitor). WARM-PATH NODES: Josh Seidenfeld (DLA Piper) = legal-partner intros (bumps on a16z/Lux/Basis Set/Bessemer, contingent on DLA); Johnny = BD / life-sciences venture-banking contact coordinating the intros. Other firms remain warm-path 1-2 pending named nodes.</t>
+          <t>Institutional Seed (raise and valuation TBD with the lead; prior working figure ~$6M; burn $60K rising to $225-300K/mo). POSITIONING per the 2026-10-02 deck: Coharts is an Applied AI company, 'the intelligence layer between a molecule and a medicine' - AI-native, IaaS drug-development infrastructure that connects raw assay to regulatory submission and simulates trial success before patient one (BEAM builds documented models, CTS runs the trial in silico, iViz analyzes). Foresight Base is the connected program record ($2K/program/mo); modules PRISM/ATHENA/BEAM/CTS/iViz switch on by stage. ICH E6(R3) governance and ICH M15 model credibility are a built-in regulatory MOAT, NOT the product. IaaS, never SaaS. $44B TAM (AI biostatistics/bioinformatics, CDMS/real-time-trial infra, RWD/patient-matching, in-silico simulation + MIDD); SAM ~$15B. Validation is RETROSPECTIVE (LEAP Phase 2, PK, failures re-run); NSCLC in PoC. Traction: Tempus POC (results for JPM Jan 2027), Synthon pilot complete ($250K-$415K paid conversion), PRISM FDA grant filed with 2 pediatric hospitals, CDA with Lilly, early talks with J&amp;J. Most check sizes Unknown pending PitchBook; emails inferred unless marked Verified. CONFLICT: Radical Ventures holds Unlearn.AI (direct competitor). WARM-PATH: Josh Seidenfeld (DLA Piper) = legal intros (a16z/Lux/Basis Set/Bessemer, contingent on DLA); Johnny = BD coordinating intros; Oncology Ventures + Care Equity = direct CRM relationships. Others warm-path 1-2 pending named nodes.</t>
         </is>
       </c>
     </row>

--- a/fundraising/coharts-seed-investor-pipeline.xlsx
+++ b/fundraising/coharts-seed-investor-pipeline.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipeline'!$A$1:$AD$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD57"/>
+  <dimension ref="A1:AD59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8505,9 +8505,281 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>NFX</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed VC (network effects; NFX Bio practice)</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA / Herzliya</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV, $325M, closed end 2024 (~$1.5B AUM)</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed and seed; leads</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>~$1.5M to $5M initial (avg $4-5M, Fund IV)</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>No (active review since Jan 2026)</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>NFX Bio (TechBio/AI-x-bio): led ImmuneBridge $8M seed (Mar 2026), co-led Cyclana Bio (Oct 2025), Mana.bio (Sep 2025), Mammoth Biosciences, C2i Genomics. IC incl. Emily Leproust (Twist CEO).</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Core NFX thesis funds AI infrastructure, data tooling, developer platforms, and vertical AI (published thesis + portfolio).</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>NFX Bio holdings are wet-biology (CRISPR, drug delivery, vaccines); no trial-sim / in-silico-outcome company. No conflict.</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>Omri Amirav-Drory, PhD (alt: James Currier, core fund)</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>General Partner &amp; Head of NFX Bio</t>
+        </is>
+      </c>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE: NFX has been reviewing Coharts' product since Jan 2026 (in-flight relationship). Work directly, not via DLA.</t>
+        </is>
+      </c>
+      <c r="Q58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W58" s="10">
+        <f>MAX(0,ROUND(Q58/5*Weights!$B$3+R58/5*Weights!$B$4+S58/5*Weights!$B$5+T58/5*Weights!$B$6+U58/5*Weights!$B$7+V58/5*Weights!$B$8-L58*Weights!$B$9,0))</f>
+        <v>98</v>
+      </c>
+      <c r="X58" s="10" t="str">
+        <f>IF(W58&gt;=Weights!$B$12,"A",IF(W58&gt;=Weights!$B$13,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="Y58" s="11" t="inlineStr">
+        <is>
+          <t>First meeting</t>
+        </is>
+      </c>
+      <c r="Z58" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA58" s="8" t="inlineStr">
+        <is>
+          <t>Drive the existing NFX review to a term sheet. Omri (NFX Bio) is the domain bridge; route the software-infra profile to the core fund (Currier) if Bio stalls on 'wet-lab only'. Confirm where the eval stands.</t>
+        </is>
+      </c>
+      <c r="AB58" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nfx.com/post/nfx-fund-iv; https://www.nfx.com/team/omri-amirav-drory</t>
+        </is>
+      </c>
+      <c r="AD58" s="8" t="inlineStr">
+        <is>
+          <t>TOP PRIORITY: thesis-perfect seed lead + active product review since Jan 2026. Caveat: NFX Bio leans wet-lab bioplatforms, so Coharts' software/regulatory-IaaS profile may fit the core AI-infra fund better. Email omri@nfx.com Inferred (first@nfx.com pattern ~85%). Move status to Diligence/Term sheet as the review advances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Fund</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>YC-alumni co-investment fund (sector-agnostic + AI/ML and Bio/Health sleeves)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Debut fund ~$20M (2018); multiple vehicles since; current flagship size Unknown</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Pre-seed/seed; co-invests alongside YC, does not lead</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>~$150K to $250K avg (some $500K-$2M)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>No (co-invests)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>Bio+Health sleeve; ~14 therapeutics holdings. Argon AI (pharma AI copilot, $5.5M seed Jul 2025), ParcelBio ($13.2M, 2026), Olio Labs, Ply Health, Resvita Bio.</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML sub-fund; Argon AI (pharma AI) among holdings.</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>Argon AI (pharma AI clinical/competitive-intelligence copilot) is a mild adjacency to the 'intelligence layer'/iViz, not a CTS/in-silico competitor.</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>Dave Messina (GP, Bio+Health) - founder's contact</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>General Partner (alt: AI Fund GPs Francesco Mosconi / Rajiv Bhat)</t>
+        </is>
+      </c>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>Founder knows Dave (likely Dave Messina, GP, Bio+Health). Direct warm node. Work directly.</t>
+        </is>
+      </c>
+      <c r="Q59" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R59" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V59" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W59" s="10">
+        <f>MAX(0,ROUND(Q59/5*Weights!$B$3+R59/5*Weights!$B$4+S59/5*Weights!$B$5+T59/5*Weights!$B$6+U59/5*Weights!$B$7+V59/5*Weights!$B$8-L59*Weights!$B$9,0))</f>
+        <v>56</v>
+      </c>
+      <c r="X59" s="10" t="str">
+        <f>IF(W59&gt;=Weights!$B$12,"A",IF(W59&gt;=Weights!$B$13,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="Y59" s="11" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="Z59" s="7" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA59" s="8" t="inlineStr">
+        <is>
+          <t>Use the Dave relationship for a read/signal, but Pioneer co-invests (not a lead), writes small checks, and gates largely to YC companies. Confirm YC eligibility; do not count on it to lead.</t>
+        </is>
+      </c>
+      <c r="AB59" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AC59" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pioneerfund.vc; https://www.crunchbase.com/organization/pioneer-fund</t>
+        </is>
+      </c>
+      <c r="AD59" s="8" t="inlineStr">
+        <is>
+          <t>YC-alumni fund (pioneerfund.vc), NOT Daniel Gross's Pioneer. Warm via 'Dave' (likely Dave Messina). Non-lead + YC gate + small checks cap the fit; the Dave relationship is why it is worth a conversation. Email pattern Unknown, do not guess.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD57"/>
-  <conditionalFormatting sqref="W2:W57">
+  <autoFilter ref="A1:AD59"/>
+  <conditionalFormatting sqref="W2:W59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -8520,14 +8792,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y2:Y257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not contacted,Researching,Intro requested,Intro made,First meeting,Diligence,Term sheet,Closed,Passed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q257 R2:R257 S2:S257 T2:T257 U2:U257 V2:V257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="Q2:Q259 R2:R259 S2:S259 T2:T259 U2:U259 V2:V259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -8728,7 +9000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10466,6 +10738,114 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>NFX</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Fund IV $325M end 2024; leads seed; $1.5-5M checks</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Calcalist / NFX</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nfx.com/post/nfx-fund-iv</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>NFX</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>NFX Bio led ImmuneBridge $8M seed (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Web search</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nfx.com/post/launching-nfx-bio</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Fund</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>YC-alumni co-investment fund; AI/ML + Bio/Health sleeves; does not lead</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Crunchbase / web</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/organization/pioneer-fund</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Fund</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Argon AI $5.5M seed Jul 2025 (Pioneer + YC)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Web search</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/organization/argon-ai</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
